--- a/research/traditional_assets/database/data/canada/canada_publishing_newspapers.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_publishing_newspapers.xlsx
@@ -1769,7 +1769,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1906,22 +1906,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08822489048636288</v>
+        <v>0.08802416952657401</v>
       </c>
       <c r="C2">
-        <v>214.1760560997215</v>
+        <v>212.335692463556</v>
       </c>
       <c r="D2">
-        <v>207.6060560997215</v>
+        <v>208.408692463556</v>
       </c>
       <c r="E2">
-        <v>-184</v>
+        <v>-181.357</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.643</v>
       </c>
       <c r="G2">
         <v>6.57</v>
@@ -1942,28 +1942,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1329429</v>
       </c>
       <c r="N2">
-        <v>33.97499999999999</v>
+        <v>33.84205709999999</v>
       </c>
       <c r="O2">
-        <v>9.003374999999998</v>
+        <v>8.968145131499998</v>
       </c>
       <c r="P2">
-        <v>24.971625</v>
+        <v>24.87391196849999</v>
       </c>
       <c r="Q2">
-        <v>31.871625</v>
+        <v>31.77391196849999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08822489048636288</v>
+        <v>0.08853986315815557</v>
       </c>
       <c r="T2">
-        <v>0.9797896186226993</v>
+        <v>0.9870638142761101</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1980,7 +1980,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>255.5608460474383</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1988,22 +1988,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08802416952657401</v>
+        <v>0.08782344856678514</v>
       </c>
       <c r="C3">
-        <v>212.335692463556</v>
+        <v>210.5015591415059</v>
       </c>
       <c r="D3">
-        <v>208.408692463556</v>
+        <v>209.2175591415059</v>
       </c>
       <c r="E3">
-        <v>-181.357</v>
+        <v>-178.714</v>
       </c>
       <c r="F3">
-        <v>2.643</v>
+        <v>5.286</v>
       </c>
       <c r="G3">
         <v>6.57</v>
@@ -2024,28 +2024,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M3">
-        <v>0.1329429</v>
+        <v>0.2658858</v>
       </c>
       <c r="N3">
-        <v>33.84205709999999</v>
+        <v>33.70911419999999</v>
       </c>
       <c r="O3">
-        <v>8.968145131499998</v>
+        <v>8.932915263</v>
       </c>
       <c r="P3">
-        <v>24.87391196849999</v>
+        <v>24.776198937</v>
       </c>
       <c r="Q3">
-        <v>31.77391196849999</v>
+        <v>31.676198937</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08853986315815557</v>
+        <v>0.08886126384365832</v>
       </c>
       <c r="T3">
-        <v>0.9870638142761101</v>
+        <v>0.9944864629020397</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -2062,7 +2062,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>255.5608460474383</v>
+        <v>127.7804230237192</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -2070,22 +2070,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08782344856678514</v>
+        <v>0.0876227276069963</v>
       </c>
       <c r="C4">
-        <v>210.5015591415059</v>
+        <v>208.6737289586826</v>
       </c>
       <c r="D4">
-        <v>209.2175591415059</v>
+        <v>210.0327289586826</v>
       </c>
       <c r="E4">
-        <v>-178.714</v>
+        <v>-176.071</v>
       </c>
       <c r="F4">
-        <v>5.286</v>
+        <v>7.929</v>
       </c>
       <c r="G4">
         <v>6.57</v>
@@ -2106,28 +2106,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M4">
-        <v>0.2658858</v>
+        <v>0.3988287</v>
       </c>
       <c r="N4">
-        <v>33.70911419999999</v>
+        <v>33.57617129999999</v>
       </c>
       <c r="O4">
-        <v>8.932915263</v>
+        <v>8.897685394499998</v>
       </c>
       <c r="P4">
-        <v>24.776198937</v>
+        <v>24.67848590549999</v>
       </c>
       <c r="Q4">
-        <v>31.676198937</v>
+        <v>31.5784859055</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08886126384365832</v>
+        <v>0.08918929134741888</v>
       </c>
       <c r="T4">
-        <v>0.9944864629020397</v>
+        <v>1.002062155829535</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>127.7804230237192</v>
+        <v>85.18694868247945</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -2152,22 +2152,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0876227276069963</v>
+        <v>0.08742200664720742</v>
       </c>
       <c r="C5">
-        <v>208.6737289586826</v>
+        <v>206.8522758796248</v>
       </c>
       <c r="D5">
-        <v>210.0327289586826</v>
+        <v>210.8542758796249</v>
       </c>
       <c r="E5">
-        <v>-176.071</v>
+        <v>-173.428</v>
       </c>
       <c r="F5">
-        <v>7.929</v>
+        <v>10.572</v>
       </c>
       <c r="G5">
         <v>6.57</v>
@@ -2188,28 +2188,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M5">
-        <v>0.3988287</v>
+        <v>0.5317716</v>
       </c>
       <c r="N5">
-        <v>33.57617129999999</v>
+        <v>33.4432284</v>
       </c>
       <c r="O5">
-        <v>8.897685394499998</v>
+        <v>8.862455526</v>
       </c>
       <c r="P5">
-        <v>24.67848590549999</v>
+        <v>24.580772874</v>
       </c>
       <c r="Q5">
-        <v>31.5784859055</v>
+        <v>31.480772874</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08918929134741888</v>
+        <v>0.08952415275750773</v>
       </c>
       <c r="T5">
-        <v>1.002062155829535</v>
+        <v>1.009795675693019</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>85.18694868247945</v>
+        <v>63.89021151185959</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -2234,22 +2234,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08742200664720742</v>
+        <v>0.08722128568741858</v>
       </c>
       <c r="C6">
-        <v>206.8522758796248</v>
+        <v>205.0372750306698</v>
       </c>
       <c r="D6">
-        <v>210.8542758796249</v>
+        <v>211.6822750306698</v>
       </c>
       <c r="E6">
-        <v>-173.428</v>
+        <v>-170.785</v>
       </c>
       <c r="F6">
-        <v>10.572</v>
+        <v>13.215</v>
       </c>
       <c r="G6">
         <v>6.57</v>
@@ -2270,28 +2270,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M6">
-        <v>0.5317716</v>
+        <v>0.6647145000000001</v>
       </c>
       <c r="N6">
-        <v>33.4432284</v>
+        <v>33.31028549999999</v>
       </c>
       <c r="O6">
-        <v>8.862455526</v>
+        <v>8.827225657499998</v>
       </c>
       <c r="P6">
-        <v>24.580772874</v>
+        <v>24.48305984249999</v>
       </c>
       <c r="Q6">
-        <v>31.480772874</v>
+        <v>31.3830598425</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08952415275750773</v>
+        <v>0.08986606388149324</v>
       </c>
       <c r="T6">
-        <v>1.009795675693019</v>
+        <v>1.017692006500998</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2308,7 +2308,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>63.89021151185959</v>
+        <v>51.11216920948766</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2316,22 +2316,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08722128568741858</v>
+        <v>0.08702056472762972</v>
       </c>
       <c r="C7">
-        <v>205.0372750306698</v>
+        <v>203.2288027228557</v>
       </c>
       <c r="D7">
-        <v>211.6822750306698</v>
+        <v>212.5168027228557</v>
       </c>
       <c r="E7">
-        <v>-170.785</v>
+        <v>-168.142</v>
       </c>
       <c r="F7">
-        <v>13.215</v>
+        <v>15.858</v>
       </c>
       <c r="G7">
         <v>6.57</v>
@@ -2352,28 +2352,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M7">
-        <v>0.6647145000000001</v>
+        <v>0.7976574000000001</v>
       </c>
       <c r="N7">
-        <v>33.31028549999999</v>
+        <v>33.1773426</v>
       </c>
       <c r="O7">
-        <v>8.827225657499998</v>
+        <v>8.791995789</v>
       </c>
       <c r="P7">
-        <v>24.48305984249999</v>
+        <v>24.385346811</v>
       </c>
       <c r="Q7">
-        <v>31.3830598425</v>
+        <v>31.285346811</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08986606388149324</v>
+        <v>0.09021524971024437</v>
       </c>
       <c r="T7">
-        <v>1.017692006500998</v>
+        <v>1.025756344347445</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>51.11216920948766</v>
+        <v>42.59347434123973</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2398,22 +2398,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.0870205647276297</v>
+        <v>0.08681984376784085</v>
       </c>
       <c r="C8">
-        <v>203.2288027228557</v>
+        <v>201.4269364753653</v>
       </c>
       <c r="D8">
-        <v>212.5168027228557</v>
+        <v>213.3579364753653</v>
       </c>
       <c r="E8">
-        <v>-168.142</v>
+        <v>-165.499</v>
       </c>
       <c r="F8">
-        <v>15.858</v>
+        <v>18.501</v>
       </c>
       <c r="G8">
         <v>6.57</v>
@@ -2434,28 +2434,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M8">
-        <v>0.7976574</v>
+        <v>0.9306002999999998</v>
       </c>
       <c r="N8">
-        <v>33.1773426</v>
+        <v>33.04439969999999</v>
       </c>
       <c r="O8">
-        <v>8.791995789</v>
+        <v>8.756765920499998</v>
       </c>
       <c r="P8">
-        <v>24.385346811</v>
+        <v>24.28763377949999</v>
       </c>
       <c r="Q8">
-        <v>31.285346811</v>
+        <v>31.1876337795</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09021524971024436</v>
+        <v>0.09057194491165682</v>
       </c>
       <c r="T8">
-        <v>1.025756344347445</v>
+        <v>1.033994108814245</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>42.59347434123973</v>
+        <v>36.5086922924912</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2480,22 +2480,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08681984376784084</v>
+        <v>0.08661912280805198</v>
       </c>
       <c r="C9">
-        <v>201.4269364753654</v>
+        <v>199.6317550395309</v>
       </c>
       <c r="D9">
-        <v>213.3579364753654</v>
+        <v>214.2057550395309</v>
       </c>
       <c r="E9">
-        <v>-165.499</v>
+        <v>-162.856</v>
       </c>
       <c r="F9">
-        <v>18.501</v>
+        <v>21.144</v>
       </c>
       <c r="G9">
         <v>6.57</v>
@@ -2516,28 +2516,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M9">
-        <v>0.9306003</v>
+        <v>1.0635432</v>
       </c>
       <c r="N9">
-        <v>33.04439969999999</v>
+        <v>32.9114568</v>
       </c>
       <c r="O9">
-        <v>8.756765920499998</v>
+        <v>8.721536051999999</v>
       </c>
       <c r="P9">
-        <v>24.28763377949999</v>
+        <v>24.189920748</v>
       </c>
       <c r="Q9">
-        <v>31.1876337795</v>
+        <v>31.089920748</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09057194491165682</v>
+        <v>0.09093639435657824</v>
       </c>
       <c r="T9">
-        <v>1.033994108814245</v>
+        <v>1.04241095511728</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2554,7 +2554,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>36.50869229249119</v>
+        <v>31.9451057559298</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2562,22 +2562,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08661912280805198</v>
+        <v>0.08641840184826312</v>
       </c>
       <c r="C10">
-        <v>199.6317550395309</v>
+        <v>197.8433384234125</v>
       </c>
       <c r="D10">
-        <v>214.2057550395309</v>
+        <v>215.0603384234125</v>
       </c>
       <c r="E10">
-        <v>-162.856</v>
+        <v>-160.213</v>
       </c>
       <c r="F10">
-        <v>21.144</v>
+        <v>23.787</v>
       </c>
       <c r="G10">
         <v>6.57</v>
@@ -2598,28 +2598,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M10">
-        <v>1.0635432</v>
+        <v>1.1964861</v>
       </c>
       <c r="N10">
-        <v>32.9114568</v>
+        <v>32.77851389999999</v>
       </c>
       <c r="O10">
-        <v>8.721536051999999</v>
+        <v>8.686306183499999</v>
       </c>
       <c r="P10">
-        <v>24.189920748</v>
+        <v>24.09220771649999</v>
       </c>
       <c r="Q10">
-        <v>31.089920748</v>
+        <v>30.99220771649999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09093639435657824</v>
+        <v>0.09130885367941002</v>
       </c>
       <c r="T10">
-        <v>1.04241095511728</v>
+        <v>1.051012787053349</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>31.9451057559298</v>
+        <v>28.39564956082648</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2644,22 +2644,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08641840184826312</v>
+        <v>0.08621768088847424</v>
       </c>
       <c r="C11">
-        <v>197.8433384234125</v>
+        <v>196.0617679169671</v>
       </c>
       <c r="D11">
-        <v>215.0603384234125</v>
+        <v>215.9217679169671</v>
       </c>
       <c r="E11">
-        <v>-160.213</v>
+        <v>-157.57</v>
       </c>
       <c r="F11">
-        <v>23.787</v>
+        <v>26.43</v>
       </c>
       <c r="G11">
         <v>6.57</v>
@@ -2680,28 +2680,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M11">
-        <v>1.1964861</v>
+        <v>1.329429</v>
       </c>
       <c r="N11">
-        <v>32.77851389999999</v>
+        <v>32.645571</v>
       </c>
       <c r="O11">
-        <v>8.686306183499999</v>
+        <v>8.651076314999999</v>
       </c>
       <c r="P11">
-        <v>24.09220771649999</v>
+        <v>23.994494685</v>
       </c>
       <c r="Q11">
-        <v>30.99220771649999</v>
+        <v>30.894494685</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09130885367941002</v>
+        <v>0.0916895898760825</v>
       </c>
       <c r="T11">
-        <v>1.051012787053349</v>
+        <v>1.05980577081022</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2718,7 +2718,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>28.39564956082648</v>
+        <v>25.55608460474384</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2726,22 +2726,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08621768088847424</v>
+        <v>0.08601695992868541</v>
       </c>
       <c r="C12">
-        <v>196.0617679169671</v>
+        <v>194.2871261178251</v>
       </c>
       <c r="D12">
-        <v>215.9217679169671</v>
+        <v>216.7901261178251</v>
       </c>
       <c r="E12">
-        <v>-157.57</v>
+        <v>-154.927</v>
       </c>
       <c r="F12">
-        <v>26.43</v>
+        <v>29.073</v>
       </c>
       <c r="G12">
         <v>6.57</v>
@@ -2762,28 +2762,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M12">
-        <v>1.329429</v>
+        <v>1.4623719</v>
       </c>
       <c r="N12">
-        <v>32.645571</v>
+        <v>32.51262809999999</v>
       </c>
       <c r="O12">
-        <v>8.651076314999999</v>
+        <v>8.615846446499999</v>
       </c>
       <c r="P12">
-        <v>23.994494685</v>
+        <v>23.89678165349999</v>
       </c>
       <c r="Q12">
-        <v>30.894494685</v>
+        <v>30.79678165349999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0916895898760825</v>
+        <v>0.09207888194234315</v>
       </c>
       <c r="T12">
-        <v>1.05980577081022</v>
+        <v>1.068796349707694</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2800,7 +2800,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>25.55608460474383</v>
+        <v>23.23280418613076</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2808,22 +2808,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08601695992868541</v>
+        <v>0.08581623896889655</v>
       </c>
       <c r="C13">
-        <v>194.2871261178251</v>
+        <v>192.5194969576923</v>
       </c>
       <c r="D13">
-        <v>216.7901261178251</v>
+        <v>217.6654969576923</v>
       </c>
       <c r="E13">
-        <v>-154.927</v>
+        <v>-152.284</v>
       </c>
       <c r="F13">
-        <v>29.073</v>
+        <v>31.716</v>
       </c>
       <c r="G13">
         <v>6.57</v>
@@ -2844,28 +2844,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M13">
-        <v>1.4623719</v>
+        <v>1.5953148</v>
       </c>
       <c r="N13">
-        <v>32.51262809999999</v>
+        <v>32.3796852</v>
       </c>
       <c r="O13">
-        <v>8.615846446499999</v>
+        <v>8.580616577999999</v>
       </c>
       <c r="P13">
-        <v>23.89678165349999</v>
+        <v>23.799068622</v>
       </c>
       <c r="Q13">
-        <v>30.79678165349999</v>
+        <v>30.699068622</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09207888194234315</v>
+        <v>0.09247702155556425</v>
       </c>
       <c r="T13">
-        <v>1.068796349707694</v>
+        <v>1.077991259943747</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2882,7 +2882,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>23.23280418613076</v>
+        <v>21.29673717061987</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2890,22 +2890,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08581623896889655</v>
+        <v>0.08561551800910767</v>
       </c>
       <c r="C14">
-        <v>192.5194969576923</v>
+        <v>190.758965729392</v>
       </c>
       <c r="D14">
-        <v>217.6654969576923</v>
+        <v>218.547965729392</v>
       </c>
       <c r="E14">
-        <v>-152.284</v>
+        <v>-149.641</v>
       </c>
       <c r="F14">
-        <v>31.716</v>
+        <v>34.359</v>
       </c>
       <c r="G14">
         <v>6.57</v>
@@ -2926,28 +2926,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M14">
-        <v>1.5953148</v>
+        <v>1.7282577</v>
       </c>
       <c r="N14">
-        <v>32.3796852</v>
+        <v>32.24674229999999</v>
       </c>
       <c r="O14">
-        <v>8.580616577999999</v>
+        <v>8.545386709499999</v>
       </c>
       <c r="P14">
-        <v>23.799068622</v>
+        <v>23.70135559049999</v>
       </c>
       <c r="Q14">
-        <v>30.699068622</v>
+        <v>30.6013555905</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09247702155556425</v>
+        <v>0.09288431380357204</v>
       </c>
       <c r="T14">
-        <v>1.077991259943747</v>
+        <v>1.087397547426606</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2964,7 +2964,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>21.29673717061987</v>
+        <v>19.65852661903372</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2972,22 +2972,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08561551800910767</v>
+        <v>0.08541479704931883</v>
       </c>
       <c r="C15">
-        <v>190.758965729392</v>
+        <v>189.0056191145692</v>
       </c>
       <c r="D15">
-        <v>218.547965729392</v>
+        <v>219.4376191145693</v>
       </c>
       <c r="E15">
-        <v>-149.641</v>
+        <v>-146.998</v>
       </c>
       <c r="F15">
-        <v>34.359</v>
+        <v>37.002</v>
       </c>
       <c r="G15">
         <v>6.57</v>
@@ -3008,28 +3008,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M15">
-        <v>1.7282577</v>
+        <v>1.8612006</v>
       </c>
       <c r="N15">
-        <v>32.24674229999999</v>
+        <v>32.11379939999999</v>
       </c>
       <c r="O15">
-        <v>8.545386709499999</v>
+        <v>8.510156840999999</v>
       </c>
       <c r="P15">
-        <v>23.70135559049999</v>
+        <v>23.60364255899999</v>
       </c>
       <c r="Q15">
-        <v>30.6013555905</v>
+        <v>30.503642559</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09288431380357204</v>
+        <v>0.09330107796432421</v>
       </c>
       <c r="T15">
-        <v>1.087397547426606</v>
+        <v>1.09702258578116</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -3046,7 +3046,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>19.65852661903372</v>
+        <v>18.2543461462456</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -3054,22 +3054,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08541479704931883</v>
+        <v>0.08521407608952994</v>
       </c>
       <c r="C16">
-        <v>189.0056191145692</v>
+        <v>187.2595452120749</v>
       </c>
       <c r="D16">
-        <v>219.4376191145693</v>
+        <v>220.3345452120749</v>
       </c>
       <c r="E16">
-        <v>-146.998</v>
+        <v>-144.355</v>
       </c>
       <c r="F16">
-        <v>37.002</v>
+        <v>39.64500000000001</v>
       </c>
       <c r="G16">
         <v>6.57</v>
@@ -3090,28 +3090,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M16">
-        <v>1.8612006</v>
+        <v>1.994143500000001</v>
       </c>
       <c r="N16">
-        <v>32.11379939999999</v>
+        <v>31.98085649999999</v>
       </c>
       <c r="O16">
-        <v>8.510156840999999</v>
+        <v>8.474926972499999</v>
       </c>
       <c r="P16">
-        <v>23.60364255899999</v>
+        <v>23.50592952749999</v>
       </c>
       <c r="Q16">
-        <v>30.503642559</v>
+        <v>30.4059295275</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09330107796432421</v>
+        <v>0.09372764834062347</v>
       </c>
       <c r="T16">
-        <v>1.09702258578116</v>
+        <v>1.106874095626408</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>18.2543461462456</v>
+        <v>17.03738973649589</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -3136,22 +3136,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08521407608952994</v>
+        <v>0.08501335512974109</v>
       </c>
       <c r="C17">
-        <v>187.2595452120749</v>
+        <v>185.5208335670463</v>
       </c>
       <c r="D17">
-        <v>220.3345452120749</v>
+        <v>221.2388335670463</v>
       </c>
       <c r="E17">
-        <v>-144.355</v>
+        <v>-141.712</v>
       </c>
       <c r="F17">
-        <v>39.645</v>
+        <v>42.288</v>
       </c>
       <c r="G17">
         <v>6.57</v>
@@ -3172,28 +3172,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M17">
-        <v>1.9941435</v>
+        <v>2.1270864</v>
       </c>
       <c r="N17">
-        <v>31.98085649999999</v>
+        <v>31.84791359999999</v>
       </c>
       <c r="O17">
-        <v>8.474926972499999</v>
+        <v>8.439697103999999</v>
       </c>
       <c r="P17">
-        <v>23.50592952749999</v>
+        <v>23.40821649599999</v>
       </c>
       <c r="Q17">
-        <v>30.4059295275</v>
+        <v>30.308216496</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09372764834062347</v>
+        <v>0.09416437515445369</v>
       </c>
       <c r="T17">
-        <v>1.106874095626408</v>
+        <v>1.116960165229877</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -3210,7 +3210,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>17.03738973649589</v>
+        <v>15.9725528779649</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -3218,22 +3218,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08501335512974109</v>
+        <v>0.08481263416995224</v>
       </c>
       <c r="C18">
-        <v>185.5208335670463</v>
+        <v>183.7895752007099</v>
       </c>
       <c r="D18">
-        <v>221.2388335670463</v>
+        <v>222.15057520071</v>
       </c>
       <c r="E18">
-        <v>-141.712</v>
+        <v>-139.069</v>
       </c>
       <c r="F18">
-        <v>42.288</v>
+        <v>44.931</v>
       </c>
       <c r="G18">
         <v>6.57</v>
@@ -3254,28 +3254,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M18">
-        <v>2.1270864</v>
+        <v>2.2600293</v>
       </c>
       <c r="N18">
-        <v>31.84791359999999</v>
+        <v>31.71497069999999</v>
       </c>
       <c r="O18">
-        <v>8.439697103999999</v>
+        <v>8.404467235499999</v>
       </c>
       <c r="P18">
-        <v>23.40821649599999</v>
+        <v>23.31050346449999</v>
       </c>
       <c r="Q18">
-        <v>30.308216496</v>
+        <v>30.2105034645</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09416437515445369</v>
+        <v>0.09461162550596655</v>
       </c>
       <c r="T18">
-        <v>1.116960165229877</v>
+        <v>1.127289272655116</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -3292,7 +3292,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>15.9725528779649</v>
+        <v>15.03299094396696</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3300,22 +3300,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08481263416995224</v>
+        <v>0.08461191321016337</v>
       </c>
       <c r="C19">
-        <v>183.7895752007099</v>
+        <v>182.0658626409221</v>
       </c>
       <c r="D19">
-        <v>222.15057520071</v>
+        <v>223.0698626409222</v>
       </c>
       <c r="E19">
-        <v>-139.069</v>
+        <v>-136.426</v>
       </c>
       <c r="F19">
-        <v>44.931</v>
+        <v>47.57400000000001</v>
       </c>
       <c r="G19">
         <v>6.57</v>
@@ -3336,28 +3336,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M19">
-        <v>2.2600293</v>
+        <v>2.3929722</v>
       </c>
       <c r="N19">
-        <v>31.71497069999999</v>
+        <v>31.5820278</v>
       </c>
       <c r="O19">
-        <v>8.404467235499999</v>
+        <v>8.369237366999998</v>
       </c>
       <c r="P19">
-        <v>23.31050346449999</v>
+        <v>23.212790433</v>
       </c>
       <c r="Q19">
-        <v>30.2105034645</v>
+        <v>30.112790433</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09461162550596655</v>
+        <v>0.09506978440263826</v>
       </c>
       <c r="T19">
-        <v>1.127289272655116</v>
+        <v>1.137870309529752</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3374,7 +3374,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>15.03299094396696</v>
+        <v>14.19782478041324</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3382,22 +3382,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08461191321016338</v>
+        <v>0.08441119225037452</v>
       </c>
       <c r="C20">
-        <v>182.0658626409221</v>
+        <v>180.3497899534714</v>
       </c>
       <c r="D20">
-        <v>223.0698626409221</v>
+        <v>223.9967899534714</v>
       </c>
       <c r="E20">
-        <v>-136.426</v>
+        <v>-133.783</v>
       </c>
       <c r="F20">
-        <v>47.574</v>
+        <v>50.21700000000001</v>
       </c>
       <c r="G20">
         <v>6.57</v>
@@ -3418,28 +3418,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M20">
-        <v>2.3929722</v>
+        <v>2.5259151</v>
       </c>
       <c r="N20">
-        <v>31.5820278</v>
+        <v>31.4490849</v>
       </c>
       <c r="O20">
-        <v>8.369237366999998</v>
+        <v>8.334007498499998</v>
       </c>
       <c r="P20">
-        <v>23.212790433</v>
+        <v>23.1150774015</v>
       </c>
       <c r="Q20">
-        <v>30.112790433</v>
+        <v>30.0150774015</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09506978440263826</v>
+        <v>0.09553925586465989</v>
       </c>
       <c r="T20">
-        <v>1.137870309529752</v>
+        <v>1.148712606574131</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>14.19782478041324</v>
+        <v>13.45057084460202</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3464,22 +3464,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08441119225037452</v>
+        <v>0.08443097129058566</v>
       </c>
       <c r="C21">
-        <v>180.3497899534714</v>
+        <v>177.6151085463709</v>
       </c>
       <c r="D21">
-        <v>223.9967899534714</v>
+        <v>223.9051085463709</v>
       </c>
       <c r="E21">
-        <v>-133.783</v>
+        <v>-131.14</v>
       </c>
       <c r="F21">
-        <v>50.21700000000001</v>
+        <v>52.86000000000001</v>
       </c>
       <c r="G21">
         <v>6.57</v>
@@ -3500,45 +3500,45 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M21">
-        <v>2.5259151</v>
+        <v>2.738148</v>
       </c>
       <c r="N21">
-        <v>31.4490849</v>
+        <v>31.236852</v>
       </c>
       <c r="O21">
-        <v>8.334007498499998</v>
+        <v>8.277765779999999</v>
       </c>
       <c r="P21">
-        <v>23.1150774015</v>
+        <v>22.95908622</v>
       </c>
       <c r="Q21">
-        <v>30.0150774015</v>
+        <v>29.85908622</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09553925586465989</v>
+        <v>0.09602046411323206</v>
       </c>
       <c r="T21">
-        <v>1.148712606574131</v>
+        <v>1.15982596104462</v>
       </c>
       <c r="U21">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V21">
         <v>0.265</v>
       </c>
       <c r="W21">
-        <v>0.0369705</v>
+        <v>0.038073</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y21">
-        <v>13.45057084460202</v>
+        <v>12.40802177238045</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3546,22 +3546,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08443097129058566</v>
+        <v>0.08424127533079678</v>
       </c>
       <c r="C22">
-        <v>177.6151085463709</v>
+        <v>175.8545065426825</v>
       </c>
       <c r="D22">
-        <v>223.9051085463709</v>
+        <v>224.7875065426825</v>
       </c>
       <c r="E22">
-        <v>-131.14</v>
+        <v>-128.497</v>
       </c>
       <c r="F22">
-        <v>52.86000000000001</v>
+        <v>55.50300000000001</v>
       </c>
       <c r="G22">
         <v>6.57</v>
@@ -3582,28 +3582,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M22">
-        <v>2.738148</v>
+        <v>2.8750554</v>
       </c>
       <c r="N22">
-        <v>31.236852</v>
+        <v>31.09994459999999</v>
       </c>
       <c r="O22">
-        <v>8.277765779999999</v>
+        <v>8.241485318999999</v>
       </c>
       <c r="P22">
-        <v>22.95908622</v>
+        <v>22.85845928099999</v>
       </c>
       <c r="Q22">
-        <v>29.85908622</v>
+        <v>29.758459281</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09602046411323206</v>
+        <v>0.09651385484910985</v>
       </c>
       <c r="T22">
-        <v>1.15982596104462</v>
+        <v>1.171220666261197</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3620,7 +3620,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>12.40802177238045</v>
+        <v>11.81716359274329</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3628,22 +3628,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08424127533079678</v>
+        <v>0.08405157937100793</v>
       </c>
       <c r="C23">
-        <v>175.8545065426825</v>
+        <v>174.1008870227238</v>
       </c>
       <c r="D23">
-        <v>224.7875065426825</v>
+        <v>225.6768870227238</v>
       </c>
       <c r="E23">
-        <v>-128.497</v>
+        <v>-125.854</v>
       </c>
       <c r="F23">
-        <v>55.503</v>
+        <v>58.146</v>
       </c>
       <c r="G23">
         <v>6.57</v>
@@ -3664,28 +3664,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M23">
-        <v>2.8750554</v>
+        <v>3.0119628</v>
       </c>
       <c r="N23">
-        <v>31.09994459999999</v>
+        <v>30.9630372</v>
       </c>
       <c r="O23">
-        <v>8.241485318999999</v>
+        <v>8.205204857999998</v>
       </c>
       <c r="P23">
-        <v>22.85845928099999</v>
+        <v>22.757832342</v>
       </c>
       <c r="Q23">
-        <v>29.758459281</v>
+        <v>29.657832342</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09651385484910985</v>
+        <v>0.09701989662949734</v>
       </c>
       <c r="T23">
-        <v>1.171220666261197</v>
+        <v>1.182907543406405</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3702,7 +3702,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.81716359274329</v>
+        <v>11.28001979307314</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3710,22 +3710,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08405157937100793</v>
+        <v>0.08386188341121907</v>
       </c>
       <c r="C24">
-        <v>174.1008870227238</v>
+        <v>172.3543331951154</v>
       </c>
       <c r="D24">
-        <v>225.6768870227238</v>
+        <v>226.5733331951154</v>
       </c>
       <c r="E24">
-        <v>-125.854</v>
+        <v>-123.211</v>
       </c>
       <c r="F24">
-        <v>58.146</v>
+        <v>60.78900000000001</v>
       </c>
       <c r="G24">
         <v>6.57</v>
@@ -3746,28 +3746,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M24">
-        <v>3.0119628</v>
+        <v>3.1488702</v>
       </c>
       <c r="N24">
-        <v>30.9630372</v>
+        <v>30.82612979999999</v>
       </c>
       <c r="O24">
-        <v>8.205204857999998</v>
+        <v>8.168924396999998</v>
       </c>
       <c r="P24">
-        <v>22.757832342</v>
+        <v>22.657205403</v>
       </c>
       <c r="Q24">
-        <v>29.657832342</v>
+        <v>29.557205403</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09701989662949734</v>
+        <v>0.09753908235223255</v>
       </c>
       <c r="T24">
-        <v>1.182907543406405</v>
+        <v>1.194897975802137</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>11.28001979307314</v>
+        <v>10.78958414989605</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3792,22 +3792,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08386188341121907</v>
+        <v>0.08367218745143019</v>
       </c>
       <c r="C25">
-        <v>172.3543331951154</v>
+        <v>170.6149295958539</v>
       </c>
       <c r="D25">
-        <v>226.5733331951154</v>
+        <v>227.476929595854</v>
       </c>
       <c r="E25">
-        <v>-123.211</v>
+        <v>-120.568</v>
       </c>
       <c r="F25">
-        <v>60.78900000000001</v>
+        <v>63.43200000000001</v>
       </c>
       <c r="G25">
         <v>6.57</v>
@@ -3828,28 +3828,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M25">
-        <v>3.1488702</v>
+        <v>3.2857776</v>
       </c>
       <c r="N25">
-        <v>30.82612979999999</v>
+        <v>30.68922239999999</v>
       </c>
       <c r="O25">
-        <v>8.168924396999998</v>
+        <v>8.132643935999999</v>
       </c>
       <c r="P25">
-        <v>22.657205403</v>
+        <v>22.556578464</v>
       </c>
       <c r="Q25">
-        <v>29.557205403</v>
+        <v>29.456578464</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09753908235223255</v>
+        <v>0.098071930857145</v>
       </c>
       <c r="T25">
-        <v>1.194897975802137</v>
+        <v>1.207203945892494</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3866,7 +3866,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>10.78958414989605</v>
+        <v>10.34001814365038</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3874,22 +3874,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08367218745143019</v>
+        <v>0.08348249149164136</v>
       </c>
       <c r="C26">
-        <v>170.6149295958539</v>
+        <v>168.8827621148864</v>
       </c>
       <c r="D26">
-        <v>227.476929595854</v>
+        <v>228.3877621148864</v>
       </c>
       <c r="E26">
-        <v>-120.568</v>
+        <v>-117.925</v>
       </c>
       <c r="F26">
-        <v>63.432</v>
+        <v>66.075</v>
       </c>
       <c r="G26">
         <v>6.57</v>
@@ -3910,28 +3910,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M26">
-        <v>3.2857776</v>
+        <v>3.422685</v>
       </c>
       <c r="N26">
-        <v>30.68922239999999</v>
+        <v>30.55231499999999</v>
       </c>
       <c r="O26">
-        <v>8.132643935999999</v>
+        <v>8.096363474999999</v>
       </c>
       <c r="P26">
-        <v>22.556578464</v>
+        <v>22.455951525</v>
       </c>
       <c r="Q26">
-        <v>29.456578464</v>
+        <v>29.355951525</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.098071930857145</v>
+        <v>0.09861898865552179</v>
       </c>
       <c r="T26">
-        <v>1.207203945892494</v>
+        <v>1.219838075185261</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3948,7 +3948,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>10.34001814365038</v>
+        <v>9.926417417904362</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3956,22 +3956,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08348249149164136</v>
+        <v>0.08361766553185246</v>
       </c>
       <c r="C27">
-        <v>168.8827621148864</v>
+        <v>165.5899738916954</v>
       </c>
       <c r="D27">
-        <v>228.3877621148864</v>
+        <v>227.7379738916954</v>
       </c>
       <c r="E27">
-        <v>-117.925</v>
+        <v>-115.282</v>
       </c>
       <c r="F27">
-        <v>66.075</v>
+        <v>68.718</v>
       </c>
       <c r="G27">
         <v>6.57</v>
@@ -3992,45 +3992,45 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M27">
-        <v>3.422685</v>
+        <v>3.676413</v>
       </c>
       <c r="N27">
-        <v>30.55231499999999</v>
+        <v>30.29858699999999</v>
       </c>
       <c r="O27">
-        <v>8.096363474999999</v>
+        <v>8.029125554999998</v>
       </c>
       <c r="P27">
-        <v>22.455951525</v>
+        <v>22.269461445</v>
       </c>
       <c r="Q27">
-        <v>29.355951525</v>
+        <v>29.169461445</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09861898865552179</v>
+        <v>0.09918083179980064</v>
       </c>
       <c r="T27">
-        <v>1.219838075185261</v>
+        <v>1.232813667431886</v>
       </c>
       <c r="U27">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V27">
         <v>0.265</v>
       </c>
       <c r="W27">
-        <v>0.038073</v>
+        <v>0.0393225</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>9.926417417904362</v>
+        <v>9.241344756424263</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -4038,22 +4038,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08361766553185246</v>
+        <v>0.08344046457206361</v>
       </c>
       <c r="C28">
-        <v>165.5899738916954</v>
+        <v>163.7995438844761</v>
       </c>
       <c r="D28">
-        <v>227.7379738916954</v>
+        <v>228.5905438844761</v>
       </c>
       <c r="E28">
-        <v>-115.282</v>
+        <v>-112.639</v>
       </c>
       <c r="F28">
-        <v>68.718</v>
+        <v>71.361</v>
       </c>
       <c r="G28">
         <v>6.57</v>
@@ -4074,28 +4074,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M28">
-        <v>3.676413</v>
+        <v>3.8178135</v>
       </c>
       <c r="N28">
-        <v>30.29858699999999</v>
+        <v>30.15718649999999</v>
       </c>
       <c r="O28">
-        <v>8.029125554999998</v>
+        <v>7.991654422499999</v>
       </c>
       <c r="P28">
-        <v>22.269461445</v>
+        <v>22.1655320775</v>
       </c>
       <c r="Q28">
-        <v>29.169461445</v>
+        <v>29.0655320775</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09918083179980064</v>
+        <v>0.09975806790693645</v>
       </c>
       <c r="T28">
-        <v>1.232813667431886</v>
+        <v>1.2461447553565</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -4112,7 +4112,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>9.241344756424263</v>
+        <v>8.899072728408548</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -4120,22 +4120,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08344046457206361</v>
+        <v>0.08326326361227475</v>
       </c>
       <c r="C29">
-        <v>163.7995438844761</v>
+        <v>162.0155213021516</v>
       </c>
       <c r="D29">
-        <v>228.5905438844761</v>
+        <v>229.4495213021516</v>
       </c>
       <c r="E29">
-        <v>-112.639</v>
+        <v>-109.996</v>
       </c>
       <c r="F29">
-        <v>71.361</v>
+        <v>74.004</v>
       </c>
       <c r="G29">
         <v>6.57</v>
@@ -4156,28 +4156,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M29">
-        <v>3.8178135</v>
+        <v>3.959214</v>
       </c>
       <c r="N29">
-        <v>30.15718649999999</v>
+        <v>30.01578599999999</v>
       </c>
       <c r="O29">
-        <v>7.991654422499999</v>
+        <v>7.954183289999999</v>
       </c>
       <c r="P29">
-        <v>22.1655320775</v>
+        <v>22.06160271</v>
       </c>
       <c r="Q29">
-        <v>29.0655320775</v>
+        <v>28.96160271</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09975806790693645</v>
+        <v>0.1003513383503816</v>
       </c>
       <c r="T29">
-        <v>1.2461447553565</v>
+        <v>1.259846151279021</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -4194,7 +4194,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.899072728408548</v>
+        <v>8.581248702393959</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -4202,22 +4202,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08326326361227475</v>
+        <v>0.08308606265248589</v>
       </c>
       <c r="C30">
-        <v>162.0155213021516</v>
+        <v>160.2379786489429</v>
       </c>
       <c r="D30">
-        <v>229.4495213021516</v>
+        <v>230.314978648943</v>
       </c>
       <c r="E30">
-        <v>-109.996</v>
+        <v>-107.353</v>
       </c>
       <c r="F30">
-        <v>74.004</v>
+        <v>76.64700000000002</v>
       </c>
       <c r="G30">
         <v>6.57</v>
@@ -4238,28 +4238,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M30">
-        <v>3.959214</v>
+        <v>4.100614500000001</v>
       </c>
       <c r="N30">
-        <v>30.01578599999999</v>
+        <v>29.8743855</v>
       </c>
       <c r="O30">
-        <v>7.954183289999999</v>
+        <v>7.916712157499999</v>
       </c>
       <c r="P30">
-        <v>22.06160271</v>
+        <v>21.95767334249999</v>
       </c>
       <c r="Q30">
-        <v>28.96160271</v>
+        <v>28.8576733425</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1003513383503816</v>
+        <v>0.1009613206373041</v>
       </c>
       <c r="T30">
-        <v>1.259846151279021</v>
+        <v>1.273933502016261</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -4276,7 +4276,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.581248702393959</v>
+        <v>8.2853435747252</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4284,22 +4284,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08308606265248589</v>
+        <v>0.08290886169269701</v>
       </c>
       <c r="C31">
-        <v>160.237978648943</v>
+        <v>158.4669895271236</v>
       </c>
       <c r="D31">
-        <v>230.314978648943</v>
+        <v>231.1869895271237</v>
       </c>
       <c r="E31">
-        <v>-107.353</v>
+        <v>-104.71</v>
       </c>
       <c r="F31">
-        <v>76.64699999999999</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="G31">
         <v>6.57</v>
@@ -4320,28 +4320,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M31">
-        <v>4.1006145</v>
+        <v>4.242015</v>
       </c>
       <c r="N31">
-        <v>29.8743855</v>
+        <v>29.73298499999999</v>
       </c>
       <c r="O31">
-        <v>7.916712157499999</v>
+        <v>7.879241024999998</v>
       </c>
       <c r="P31">
-        <v>21.95767334249999</v>
+        <v>21.85374397499999</v>
       </c>
       <c r="Q31">
-        <v>28.8576733425</v>
+        <v>28.753743975</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1009613206373041</v>
+        <v>0.1015887309895672</v>
       </c>
       <c r="T31">
-        <v>1.273933502016261</v>
+        <v>1.288423348488849</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -4358,7 +4358,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.285343574725202</v>
+        <v>8.009165455567693</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4366,22 +4366,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08290886169269701</v>
+        <v>0.08273166073290816</v>
       </c>
       <c r="C32">
-        <v>158.4669895271236</v>
+        <v>156.7026286578853</v>
       </c>
       <c r="D32">
-        <v>231.1869895271237</v>
+        <v>232.0656286578853</v>
       </c>
       <c r="E32">
-        <v>-104.71</v>
+        <v>-102.067</v>
       </c>
       <c r="F32">
-        <v>79.29000000000001</v>
+        <v>81.93300000000001</v>
       </c>
       <c r="G32">
         <v>6.57</v>
@@ -4402,28 +4402,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M32">
-        <v>4.242015</v>
+        <v>4.3834155</v>
       </c>
       <c r="N32">
-        <v>29.73298499999999</v>
+        <v>29.5915845</v>
       </c>
       <c r="O32">
-        <v>7.879241024999998</v>
+        <v>7.841769892499999</v>
       </c>
       <c r="P32">
-        <v>21.85374397499999</v>
+        <v>21.7498146075</v>
       </c>
       <c r="Q32">
-        <v>28.753743975</v>
+        <v>28.6498146075</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1015887309895672</v>
+        <v>0.1022343271491423</v>
       </c>
       <c r="T32">
-        <v>1.288423348488849</v>
+        <v>1.303333190511369</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -4440,7 +4440,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.009165455567693</v>
+        <v>7.75080527958164</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4448,22 +4448,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08273166073290816</v>
+        <v>0.08274261977311929</v>
       </c>
       <c r="C33">
-        <v>156.7026286578853</v>
+        <v>154.0050952854351</v>
       </c>
       <c r="D33">
-        <v>232.0656286578853</v>
+        <v>232.0110952854351</v>
       </c>
       <c r="E33">
-        <v>-102.067</v>
+        <v>-99.42399999999999</v>
       </c>
       <c r="F33">
-        <v>81.93300000000001</v>
+        <v>84.57600000000001</v>
       </c>
       <c r="G33">
         <v>6.57</v>
@@ -4484,45 +4484,45 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M33">
-        <v>4.3834155</v>
+        <v>4.592476800000001</v>
       </c>
       <c r="N33">
-        <v>29.5915845</v>
+        <v>29.38252319999999</v>
       </c>
       <c r="O33">
-        <v>7.841769892499999</v>
+        <v>7.786368647999999</v>
       </c>
       <c r="P33">
-        <v>21.7498146075</v>
+        <v>21.59615455199999</v>
       </c>
       <c r="Q33">
-        <v>28.6498146075</v>
+        <v>28.496154552</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1022343271491423</v>
+        <v>0.1028989114310578</v>
       </c>
       <c r="T33">
-        <v>1.303333190511369</v>
+        <v>1.318681557299257</v>
       </c>
       <c r="U33">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V33">
         <v>0.265</v>
       </c>
       <c r="W33">
-        <v>0.0393225</v>
+        <v>0.0399105</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y33">
-        <v>7.75080527958164</v>
+        <v>7.39796878233549</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4530,22 +4530,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08274261977311929</v>
+        <v>0.08257129881333045</v>
       </c>
       <c r="C34">
-        <v>154.0050952854351</v>
+        <v>152.2175492045589</v>
       </c>
       <c r="D34">
-        <v>232.0110952854351</v>
+        <v>232.8665492045589</v>
       </c>
       <c r="E34">
-        <v>-99.42399999999999</v>
+        <v>-96.78099999999999</v>
       </c>
       <c r="F34">
-        <v>84.57600000000001</v>
+        <v>87.21900000000001</v>
       </c>
       <c r="G34">
         <v>6.57</v>
@@ -4566,28 +4566,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M34">
-        <v>4.592476800000001</v>
+        <v>4.7359917</v>
       </c>
       <c r="N34">
-        <v>29.38252319999999</v>
+        <v>29.23900829999999</v>
       </c>
       <c r="O34">
-        <v>7.786368647999999</v>
+        <v>7.748337199499999</v>
       </c>
       <c r="P34">
-        <v>21.59615455199999</v>
+        <v>21.49067110049999</v>
       </c>
       <c r="Q34">
-        <v>28.496154552</v>
+        <v>28.3906711005</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1028989114310578</v>
+        <v>0.1035833340497469</v>
       </c>
       <c r="T34">
-        <v>1.318681557299257</v>
+        <v>1.334488084289768</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4604,7 +4604,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.39796878233549</v>
+        <v>7.173787910143506</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4612,22 +4612,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08257129881333045</v>
+        <v>0.08239997785354158</v>
       </c>
       <c r="C35">
-        <v>152.2175492045589</v>
+        <v>150.4363348004994</v>
       </c>
       <c r="D35">
-        <v>232.8665492045589</v>
+        <v>233.7283348004995</v>
       </c>
       <c r="E35">
-        <v>-96.78099999999999</v>
+        <v>-94.13799999999999</v>
       </c>
       <c r="F35">
-        <v>87.21900000000001</v>
+        <v>89.86200000000001</v>
       </c>
       <c r="G35">
         <v>6.57</v>
@@ -4648,28 +4648,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M35">
-        <v>4.7359917</v>
+        <v>4.879506600000001</v>
       </c>
       <c r="N35">
-        <v>29.23900829999999</v>
+        <v>29.0954934</v>
       </c>
       <c r="O35">
-        <v>7.748337199499999</v>
+        <v>7.710305750999999</v>
       </c>
       <c r="P35">
-        <v>21.49067110049999</v>
+        <v>21.385187649</v>
       </c>
       <c r="Q35">
-        <v>28.3906711005</v>
+        <v>28.285187649</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1035833340497469</v>
+        <v>0.1042884967477903</v>
       </c>
       <c r="T35">
-        <v>1.334488084289768</v>
+        <v>1.350773596946658</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4686,7 +4686,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>7.173787910143506</v>
+        <v>6.962794148080461</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4694,22 +4694,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08239997785354158</v>
+        <v>0.08222865689375272</v>
       </c>
       <c r="C36">
-        <v>150.4363348004994</v>
+        <v>148.6615226306167</v>
       </c>
       <c r="D36">
-        <v>233.7283348004995</v>
+        <v>234.5965226306167</v>
       </c>
       <c r="E36">
-        <v>-94.13799999999999</v>
+        <v>-91.49499999999999</v>
       </c>
       <c r="F36">
-        <v>89.86200000000001</v>
+        <v>92.50500000000001</v>
       </c>
       <c r="G36">
         <v>6.57</v>
@@ -4730,28 +4730,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M36">
-        <v>4.879506600000001</v>
+        <v>5.0230215</v>
       </c>
       <c r="N36">
-        <v>29.0954934</v>
+        <v>28.9519785</v>
       </c>
       <c r="O36">
-        <v>7.710305750999999</v>
+        <v>7.672274302499999</v>
       </c>
       <c r="P36">
-        <v>21.385187649</v>
+        <v>21.2797041975</v>
       </c>
       <c r="Q36">
-        <v>28.285187649</v>
+        <v>28.1797041975</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1042884967477903</v>
+        <v>0.1050153567596196</v>
       </c>
       <c r="T36">
-        <v>1.350773596946658</v>
+        <v>1.367560202300683</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4768,7 +4768,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.962794148080461</v>
+        <v>6.76385717242102</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4776,22 +4776,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08222865689375272</v>
+        <v>0.08205733593396385</v>
       </c>
       <c r="C37">
-        <v>148.6615226306167</v>
+        <v>146.8931843045254</v>
       </c>
       <c r="D37">
-        <v>234.5965226306167</v>
+        <v>235.4711843045255</v>
       </c>
       <c r="E37">
-        <v>-91.49499999999999</v>
+        <v>-88.85199999999999</v>
       </c>
       <c r="F37">
-        <v>92.50500000000001</v>
+        <v>95.14800000000001</v>
       </c>
       <c r="G37">
         <v>6.57</v>
@@ -4812,28 +4812,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M37">
-        <v>5.0230215</v>
+        <v>5.166536400000001</v>
       </c>
       <c r="N37">
-        <v>28.9519785</v>
+        <v>28.80846359999999</v>
       </c>
       <c r="O37">
-        <v>7.672274302499999</v>
+        <v>7.634242853999998</v>
       </c>
       <c r="P37">
-        <v>21.2797041975</v>
+        <v>21.174220746</v>
       </c>
       <c r="Q37">
-        <v>28.1797041975</v>
+        <v>28.074220746</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1050153567596196</v>
+        <v>0.1057649311468185</v>
       </c>
       <c r="T37">
-        <v>1.367560202300683</v>
+        <v>1.384871389072022</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4850,7 +4850,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.76385717242102</v>
+        <v>6.57597225096488</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4858,22 +4858,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08205733593396386</v>
+        <v>0.081886014974175</v>
       </c>
       <c r="C38">
-        <v>146.8931843045254</v>
+        <v>145.1313925037841</v>
       </c>
       <c r="D38">
-        <v>235.4711843045254</v>
+        <v>236.3523925037841</v>
       </c>
       <c r="E38">
-        <v>-88.852</v>
+        <v>-86.209</v>
       </c>
       <c r="F38">
-        <v>95.148</v>
+        <v>97.791</v>
       </c>
       <c r="G38">
         <v>6.57</v>
@@ -4894,28 +4894,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M38">
-        <v>5.1665364</v>
+        <v>5.3100513</v>
       </c>
       <c r="N38">
-        <v>28.8084636</v>
+        <v>28.6649487</v>
       </c>
       <c r="O38">
-        <v>7.634242853999999</v>
+        <v>7.596211405499999</v>
       </c>
       <c r="P38">
-        <v>21.174220746</v>
+        <v>21.0687372945</v>
       </c>
       <c r="Q38">
-        <v>28.074220746</v>
+        <v>27.9687372945</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1057649311468185</v>
+        <v>0.1065383015463095</v>
       </c>
       <c r="T38">
-        <v>1.384871389072022</v>
+        <v>1.402732137328164</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4932,7 +4932,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.575972250964882</v>
+        <v>6.398243271209075</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4940,22 +4940,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.081886014974175</v>
+        <v>0.08171469401438614</v>
       </c>
       <c r="C39">
-        <v>145.1313925037841</v>
+        <v>143.3762210020285</v>
       </c>
       <c r="D39">
-        <v>236.3523925037841</v>
+        <v>237.2402210020285</v>
       </c>
       <c r="E39">
-        <v>-86.209</v>
+        <v>-83.56599999999999</v>
       </c>
       <c r="F39">
-        <v>97.791</v>
+        <v>100.434</v>
       </c>
       <c r="G39">
         <v>6.57</v>
@@ -4976,28 +4976,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M39">
-        <v>5.3100513</v>
+        <v>5.453566200000001</v>
       </c>
       <c r="N39">
-        <v>28.6649487</v>
+        <v>28.52143379999999</v>
       </c>
       <c r="O39">
-        <v>7.596211405499999</v>
+        <v>7.558179956999998</v>
       </c>
       <c r="P39">
-        <v>21.0687372945</v>
+        <v>20.963253843</v>
       </c>
       <c r="Q39">
-        <v>27.9687372945</v>
+        <v>27.863253843</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1065383015463095</v>
+        <v>0.1073366193780421</v>
       </c>
       <c r="T39">
-        <v>1.402732137328164</v>
+        <v>1.42116903875386</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -5014,7 +5014,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.398243271209075</v>
+        <v>6.229868448282518</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -5022,22 +5022,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08171469401438614</v>
+        <v>0.08183002305459727</v>
       </c>
       <c r="C40">
-        <v>143.3762210020285</v>
+        <v>140.1348248899292</v>
       </c>
       <c r="D40">
-        <v>237.2402210020285</v>
+        <v>236.6418248899293</v>
       </c>
       <c r="E40">
-        <v>-83.56599999999999</v>
+        <v>-80.92299999999999</v>
       </c>
       <c r="F40">
-        <v>100.434</v>
+        <v>103.077</v>
       </c>
       <c r="G40">
         <v>6.57</v>
@@ -5058,45 +5058,45 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M40">
-        <v>5.453566200000001</v>
+        <v>5.700158100000001</v>
       </c>
       <c r="N40">
-        <v>28.52143379999999</v>
+        <v>28.27484189999999</v>
       </c>
       <c r="O40">
-        <v>7.558179956999998</v>
+        <v>7.492833103499998</v>
       </c>
       <c r="P40">
-        <v>20.963253843</v>
+        <v>20.78200879649999</v>
       </c>
       <c r="Q40">
-        <v>27.863253843</v>
+        <v>27.6820087965</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1073366193780421</v>
+        <v>0.1081611115649136</v>
       </c>
       <c r="T40">
-        <v>1.42116903875386</v>
+        <v>1.440210428750891</v>
       </c>
       <c r="U40">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V40">
         <v>0.265</v>
       </c>
       <c r="W40">
-        <v>0.0399105</v>
+        <v>0.0406455</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y40">
-        <v>6.229868448282518</v>
+        <v>5.960360994197685</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -5104,22 +5104,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08183002305459727</v>
+        <v>0.08166605209480841</v>
       </c>
       <c r="C41">
-        <v>140.1348248899292</v>
+        <v>138.3435127471179</v>
       </c>
       <c r="D41">
-        <v>236.6418248899293</v>
+        <v>237.4935127471179</v>
       </c>
       <c r="E41">
-        <v>-80.92299999999999</v>
+        <v>-78.27999999999999</v>
       </c>
       <c r="F41">
-        <v>103.077</v>
+        <v>105.72</v>
       </c>
       <c r="G41">
         <v>6.57</v>
@@ -5140,28 +5140,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M41">
-        <v>5.700158100000001</v>
+        <v>5.846316000000001</v>
       </c>
       <c r="N41">
-        <v>28.27484189999999</v>
+        <v>28.12868399999999</v>
       </c>
       <c r="O41">
-        <v>7.492833103499998</v>
+        <v>7.454101259999998</v>
       </c>
       <c r="P41">
-        <v>20.78200879649999</v>
+        <v>20.67458273999999</v>
       </c>
       <c r="Q41">
-        <v>27.6820087965</v>
+        <v>27.57458274</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1081611115649136</v>
+        <v>0.1090130868246807</v>
       </c>
       <c r="T41">
-        <v>1.440210428750891</v>
+        <v>1.459886531747822</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -5178,7 +5178,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.960360994197685</v>
+        <v>5.811351969342743</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -5186,22 +5186,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08166605209480841</v>
+        <v>0.08150208113501954</v>
       </c>
       <c r="C42">
-        <v>138.3435127471179</v>
+        <v>136.5583532976738</v>
       </c>
       <c r="D42">
-        <v>237.4935127471179</v>
+        <v>238.3513532976739</v>
       </c>
       <c r="E42">
-        <v>-78.27999999999999</v>
+        <v>-75.63699999999999</v>
       </c>
       <c r="F42">
-        <v>105.72</v>
+        <v>108.363</v>
       </c>
       <c r="G42">
         <v>6.57</v>
@@ -5222,28 +5222,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M42">
-        <v>5.846316000000001</v>
+        <v>5.992473900000001</v>
       </c>
       <c r="N42">
-        <v>28.12868399999999</v>
+        <v>27.98252609999999</v>
       </c>
       <c r="O42">
-        <v>7.454101259999998</v>
+        <v>7.415369416499999</v>
       </c>
       <c r="P42">
-        <v>20.67458273999999</v>
+        <v>20.5671566835</v>
       </c>
       <c r="Q42">
-        <v>27.57458274</v>
+        <v>27.4671566835</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1090130868246807</v>
+        <v>0.1098939426017281</v>
       </c>
       <c r="T42">
-        <v>1.459886531747822</v>
+        <v>1.480229621287022</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -5260,7 +5260,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.811351969342743</v>
+        <v>5.669611677407555</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5268,22 +5268,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08150208113501954</v>
+        <v>0.08133811017523068</v>
       </c>
       <c r="C43">
-        <v>136.5583532976738</v>
+        <v>134.7794134549639</v>
       </c>
       <c r="D43">
-        <v>238.3513532976739</v>
+        <v>239.2154134549639</v>
       </c>
       <c r="E43">
-        <v>-75.63699999999999</v>
+        <v>-72.99399999999999</v>
       </c>
       <c r="F43">
-        <v>108.363</v>
+        <v>111.006</v>
       </c>
       <c r="G43">
         <v>6.57</v>
@@ -5304,28 +5304,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M43">
-        <v>5.992473900000001</v>
+        <v>6.138631800000001</v>
       </c>
       <c r="N43">
-        <v>27.98252609999999</v>
+        <v>27.8363682</v>
       </c>
       <c r="O43">
-        <v>7.415369416499999</v>
+        <v>7.376637572999999</v>
       </c>
       <c r="P43">
-        <v>20.5671566835</v>
+        <v>20.459730627</v>
       </c>
       <c r="Q43">
-        <v>27.4671566835</v>
+        <v>27.359730627</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1098939426017281</v>
+        <v>0.110805172715915</v>
       </c>
       <c r="T43">
-        <v>1.480229621287022</v>
+        <v>1.501274196672401</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -5342,7 +5342,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.669611677407555</v>
+        <v>5.534620923183565</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5350,22 +5350,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.0813381101752307</v>
+        <v>0.08117413921544184</v>
       </c>
       <c r="C44">
-        <v>134.7794134549638</v>
+        <v>133.0067611061702</v>
       </c>
       <c r="D44">
-        <v>239.2154134549639</v>
+        <v>240.0857611061703</v>
       </c>
       <c r="E44">
-        <v>-72.994</v>
+        <v>-70.351</v>
       </c>
       <c r="F44">
-        <v>111.006</v>
+        <v>113.649</v>
       </c>
       <c r="G44">
         <v>6.57</v>
@@ -5386,28 +5386,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M44">
-        <v>6.138631800000001</v>
+        <v>6.2847897</v>
       </c>
       <c r="N44">
-        <v>27.8363682</v>
+        <v>27.69021029999999</v>
       </c>
       <c r="O44">
-        <v>7.376637572999999</v>
+        <v>7.337905729499998</v>
       </c>
       <c r="P44">
-        <v>20.459730627</v>
+        <v>20.3523045705</v>
       </c>
       <c r="Q44">
-        <v>27.359730627</v>
+        <v>27.2523045705</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.110805172715915</v>
+        <v>0.1117483758165646</v>
       </c>
       <c r="T44">
-        <v>1.501274196672401</v>
+        <v>1.523057178211654</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -5424,7 +5424,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.534620923183565</v>
+        <v>5.405908808690924</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5432,22 +5432,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08117413921544184</v>
+        <v>0.08101016825565298</v>
       </c>
       <c r="C45">
-        <v>133.0067611061702</v>
+        <v>131.2404651300702</v>
       </c>
       <c r="D45">
-        <v>240.0857611061703</v>
+        <v>240.9624651300703</v>
       </c>
       <c r="E45">
-        <v>-70.351</v>
+        <v>-67.708</v>
       </c>
       <c r="F45">
-        <v>113.649</v>
+        <v>116.292</v>
       </c>
       <c r="G45">
         <v>6.57</v>
@@ -5468,28 +5468,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M45">
-        <v>6.2847897</v>
+        <v>6.430947600000001</v>
       </c>
       <c r="N45">
-        <v>27.69021029999999</v>
+        <v>27.54405239999999</v>
       </c>
       <c r="O45">
-        <v>7.337905729499998</v>
+        <v>7.299173885999999</v>
       </c>
       <c r="P45">
-        <v>20.3523045705</v>
+        <v>20.244878514</v>
       </c>
       <c r="Q45">
-        <v>27.2523045705</v>
+        <v>27.144878514</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1117483758165646</v>
+        <v>0.1127252647422375</v>
       </c>
       <c r="T45">
-        <v>1.523057178211654</v>
+        <v>1.545618123377308</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5506,7 +5506,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.405908808690924</v>
+        <v>5.283047244857039</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5514,22 +5514,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08101016825565298</v>
+        <v>0.08084619729586412</v>
       </c>
       <c r="C46">
-        <v>131.2404651300702</v>
+        <v>129.4805954152072</v>
       </c>
       <c r="D46">
-        <v>240.9624651300703</v>
+        <v>241.8455954152072</v>
       </c>
       <c r="E46">
-        <v>-67.708</v>
+        <v>-65.065</v>
       </c>
       <c r="F46">
-        <v>116.292</v>
+        <v>118.935</v>
       </c>
       <c r="G46">
         <v>6.57</v>
@@ -5550,28 +5550,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M46">
-        <v>6.430947600000001</v>
+        <v>6.5771055</v>
       </c>
       <c r="N46">
-        <v>27.54405239999999</v>
+        <v>27.39789449999999</v>
       </c>
       <c r="O46">
-        <v>7.299173885999999</v>
+        <v>7.260442042499998</v>
       </c>
       <c r="P46">
-        <v>20.244878514</v>
+        <v>20.13745245749999</v>
       </c>
       <c r="Q46">
-        <v>27.144878514</v>
+        <v>27.0374524575</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1127252647422375</v>
+        <v>0.1137376769015711</v>
       </c>
       <c r="T46">
-        <v>1.545618123377308</v>
+        <v>1.568999466548986</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5588,7 +5588,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.283047244857039</v>
+        <v>5.165646194971328</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5596,22 +5596,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08084619729586412</v>
+        <v>0.08068222633607525</v>
       </c>
       <c r="C47">
-        <v>129.4805954152072</v>
+        <v>127.7272228784626</v>
       </c>
       <c r="D47">
-        <v>241.8455954152072</v>
+        <v>242.7352228784626</v>
       </c>
       <c r="E47">
-        <v>-65.065</v>
+        <v>-62.42199999999998</v>
       </c>
       <c r="F47">
-        <v>118.935</v>
+        <v>121.578</v>
       </c>
       <c r="G47">
         <v>6.57</v>
@@ -5632,28 +5632,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M47">
-        <v>6.5771055</v>
+        <v>6.723263400000001</v>
       </c>
       <c r="N47">
-        <v>27.39789449999999</v>
+        <v>27.25173659999999</v>
       </c>
       <c r="O47">
-        <v>7.260442042499998</v>
+        <v>7.221710198999999</v>
       </c>
       <c r="P47">
-        <v>20.13745245749999</v>
+        <v>20.03002640099999</v>
       </c>
       <c r="Q47">
-        <v>27.0374524575</v>
+        <v>26.930026401</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1137376769015711</v>
+        <v>0.1147875858075467</v>
       </c>
       <c r="T47">
-        <v>1.568999466548986</v>
+        <v>1.593246785393689</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5670,7 +5670,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.165646194971328</v>
+        <v>5.053349538558907</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5678,22 +5678,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08068222633607525</v>
+        <v>0.08051825537628639</v>
       </c>
       <c r="C48">
-        <v>127.7272228784626</v>
+        <v>125.9804194840397</v>
       </c>
       <c r="D48">
-        <v>242.7352228784626</v>
+        <v>243.6314194840398</v>
       </c>
       <c r="E48">
-        <v>-62.42199999999998</v>
+        <v>-59.77899999999998</v>
       </c>
       <c r="F48">
-        <v>121.578</v>
+        <v>124.221</v>
       </c>
       <c r="G48">
         <v>6.57</v>
@@ -5714,28 +5714,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M48">
-        <v>6.723263400000001</v>
+        <v>6.869421300000001</v>
       </c>
       <c r="N48">
-        <v>27.25173659999999</v>
+        <v>27.1055787</v>
       </c>
       <c r="O48">
-        <v>7.221710198999999</v>
+        <v>7.1829783555</v>
       </c>
       <c r="P48">
-        <v>20.03002640099999</v>
+        <v>19.9226003445</v>
       </c>
       <c r="Q48">
-        <v>26.930026401</v>
+        <v>26.8226003445</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1147875858075467</v>
+        <v>0.1158771139175215</v>
       </c>
       <c r="T48">
-        <v>1.593246785393689</v>
+        <v>1.618409097402344</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5752,7 +5752,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.053349538558907</v>
+        <v>4.94583146327042</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5760,22 +5760,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08051825537628639</v>
+        <v>0.08035428441649753</v>
       </c>
       <c r="C49">
-        <v>125.9804194840397</v>
+        <v>124.2402582628693</v>
       </c>
       <c r="D49">
-        <v>243.6314194840398</v>
+        <v>244.5342582628693</v>
       </c>
       <c r="E49">
-        <v>-59.77899999999998</v>
+        <v>-57.13599999999998</v>
       </c>
       <c r="F49">
-        <v>124.221</v>
+        <v>126.864</v>
       </c>
       <c r="G49">
         <v>6.57</v>
@@ -5796,28 +5796,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M49">
-        <v>6.869421300000001</v>
+        <v>7.015579200000001</v>
       </c>
       <c r="N49">
-        <v>27.1055787</v>
+        <v>26.95942079999999</v>
       </c>
       <c r="O49">
-        <v>7.1829783555</v>
+        <v>7.144246511999999</v>
       </c>
       <c r="P49">
-        <v>19.9226003445</v>
+        <v>19.81517428799999</v>
       </c>
       <c r="Q49">
-        <v>26.8226003445</v>
+        <v>26.715174288</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1158771139175215</v>
+        <v>0.1170085469548029</v>
       </c>
       <c r="T49">
-        <v>1.618409097402344</v>
+        <v>1.6445391906421</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5834,7 +5834,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.94583146327042</v>
+        <v>4.84279330778562</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5842,22 +5842,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08035428441649753</v>
+        <v>0.08019031345670866</v>
       </c>
       <c r="C50">
-        <v>124.2402582628693</v>
+        <v>122.5068133324479</v>
       </c>
       <c r="D50">
-        <v>244.5342582628693</v>
+        <v>245.4438133324479</v>
       </c>
       <c r="E50">
-        <v>-57.136</v>
+        <v>-54.49299999999999</v>
       </c>
       <c r="F50">
-        <v>126.864</v>
+        <v>129.507</v>
       </c>
       <c r="G50">
         <v>6.57</v>
@@ -5878,28 +5878,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M50">
-        <v>7.0155792</v>
+        <v>7.161737100000001</v>
       </c>
       <c r="N50">
-        <v>26.95942079999999</v>
+        <v>26.81326289999999</v>
       </c>
       <c r="O50">
-        <v>7.144246511999999</v>
+        <v>7.105514668499999</v>
       </c>
       <c r="P50">
-        <v>19.81517428799999</v>
+        <v>19.70774823149999</v>
       </c>
       <c r="Q50">
-        <v>26.715174288</v>
+        <v>26.6077482315</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1170085469548029</v>
+        <v>0.118184349915115</v>
       </c>
       <c r="T50">
-        <v>1.6445391906421</v>
+        <v>1.67169399342067</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5916,7 +5916,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.84279330778562</v>
+        <v>4.743960791300199</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5924,22 +5924,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08019031345670866</v>
+        <v>0.0800263424969198</v>
       </c>
       <c r="C51">
-        <v>122.5068133324479</v>
+        <v>120.7801599171213</v>
       </c>
       <c r="D51">
-        <v>245.4438133324479</v>
+        <v>246.3601599171213</v>
       </c>
       <c r="E51">
-        <v>-54.49299999999999</v>
+        <v>-51.84999999999999</v>
       </c>
       <c r="F51">
-        <v>129.507</v>
+        <v>132.15</v>
       </c>
       <c r="G51">
         <v>6.57</v>
@@ -5960,28 +5960,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M51">
-        <v>7.161737100000001</v>
+        <v>7.307895</v>
       </c>
       <c r="N51">
-        <v>26.81326289999999</v>
+        <v>26.66710499999999</v>
       </c>
       <c r="O51">
-        <v>7.105514668499999</v>
+        <v>7.066782824999998</v>
       </c>
       <c r="P51">
-        <v>19.70774823149999</v>
+        <v>19.600322175</v>
       </c>
       <c r="Q51">
-        <v>26.6077482315</v>
+        <v>26.500322175</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.118184349915115</v>
+        <v>0.1194071849938396</v>
       </c>
       <c r="T51">
-        <v>1.67169399342067</v>
+        <v>1.699934988310383</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.743960791300199</v>
+        <v>4.649081575474195</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -6006,22 +6006,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.0800263424969198</v>
+        <v>0.07986237153713094</v>
       </c>
       <c r="C52">
-        <v>120.7801599171213</v>
+        <v>119.0603743688233</v>
       </c>
       <c r="D52">
-        <v>246.3601599171213</v>
+        <v>247.2833743688233</v>
       </c>
       <c r="E52">
-        <v>-51.84999999999999</v>
+        <v>-49.20699999999999</v>
       </c>
       <c r="F52">
-        <v>132.15</v>
+        <v>134.793</v>
       </c>
       <c r="G52">
         <v>6.57</v>
@@ -6042,28 +6042,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M52">
-        <v>7.307895</v>
+        <v>7.454052900000001</v>
       </c>
       <c r="N52">
-        <v>26.66710499999999</v>
+        <v>26.52094709999999</v>
       </c>
       <c r="O52">
-        <v>7.066782824999998</v>
+        <v>7.028050981499999</v>
       </c>
       <c r="P52">
-        <v>19.600322175</v>
+        <v>19.4928961185</v>
       </c>
       <c r="Q52">
-        <v>26.500322175</v>
+        <v>26.3928961185</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1194071849938396</v>
+        <v>0.1206799317084305</v>
       </c>
       <c r="T52">
-        <v>1.699934988310383</v>
+        <v>1.729328676869064</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -6080,7 +6080,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.649081575474195</v>
+        <v>4.557923113209995</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -6088,22 +6088,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07986237153713094</v>
+        <v>0.08065390057734208</v>
       </c>
       <c r="C53">
-        <v>119.0603743688233</v>
+        <v>112.0235682017674</v>
       </c>
       <c r="D53">
-        <v>247.2833743688233</v>
+        <v>242.8895682017674</v>
       </c>
       <c r="E53">
-        <v>-49.20699999999999</v>
+        <v>-46.56399999999999</v>
       </c>
       <c r="F53">
-        <v>134.793</v>
+        <v>137.436</v>
       </c>
       <c r="G53">
         <v>6.57</v>
@@ -6124,45 +6124,45 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M53">
-        <v>7.454052900000001</v>
+        <v>7.943800800000001</v>
       </c>
       <c r="N53">
-        <v>26.52094709999999</v>
+        <v>26.03119919999999</v>
       </c>
       <c r="O53">
-        <v>7.028050981499999</v>
+        <v>6.898267787999998</v>
       </c>
       <c r="P53">
-        <v>19.4928961185</v>
+        <v>19.13293141199999</v>
       </c>
       <c r="Q53">
-        <v>26.3928961185</v>
+        <v>26.032931412</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1206799317084305</v>
+        <v>0.1220057095361293</v>
       </c>
       <c r="T53">
-        <v>1.729328676869064</v>
+        <v>1.759947102451024</v>
       </c>
       <c r="U53">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V53">
         <v>0.265</v>
       </c>
       <c r="W53">
-        <v>0.0406455</v>
+        <v>0.042483</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y53">
-        <v>4.557923113209995</v>
+        <v>4.276919934850328</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -6170,22 +6170,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08065390057734208</v>
+        <v>0.08050830461755321</v>
       </c>
       <c r="C54">
-        <v>112.0235682017674</v>
+        <v>110.1770191977059</v>
       </c>
       <c r="D54">
-        <v>242.8895682017674</v>
+        <v>243.6860191977059</v>
       </c>
       <c r="E54">
-        <v>-46.56399999999999</v>
+        <v>-43.92099999999999</v>
       </c>
       <c r="F54">
-        <v>137.436</v>
+        <v>140.079</v>
       </c>
       <c r="G54">
         <v>6.57</v>
@@ -6206,28 +6206,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M54">
-        <v>7.943800800000001</v>
+        <v>8.096566200000002</v>
       </c>
       <c r="N54">
-        <v>26.03119919999999</v>
+        <v>25.87843379999999</v>
       </c>
       <c r="O54">
-        <v>6.898267787999998</v>
+        <v>6.857784956999998</v>
       </c>
       <c r="P54">
-        <v>19.13293141199999</v>
+        <v>19.020648843</v>
       </c>
       <c r="Q54">
-        <v>26.032931412</v>
+        <v>25.920648843</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1220057095361293</v>
+        <v>0.1233879034416026</v>
       </c>
       <c r="T54">
-        <v>1.759947102451024</v>
+        <v>1.791868439759875</v>
       </c>
       <c r="U54">
         <v>0.0578</v>
@@ -6244,7 +6244,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.276919934850328</v>
+        <v>4.196223332305983</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6252,22 +6252,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08050830461755321</v>
+        <v>0.08036270865776435</v>
       </c>
       <c r="C55">
-        <v>110.1770191977059</v>
+        <v>108.3357106085415</v>
       </c>
       <c r="D55">
-        <v>243.6860191977059</v>
+        <v>244.4877106085415</v>
       </c>
       <c r="E55">
-        <v>-43.92099999999999</v>
+        <v>-41.27799999999999</v>
       </c>
       <c r="F55">
-        <v>140.079</v>
+        <v>142.722</v>
       </c>
       <c r="G55">
         <v>6.57</v>
@@ -6288,28 +6288,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M55">
-        <v>8.096566200000002</v>
+        <v>8.249331600000001</v>
       </c>
       <c r="N55">
-        <v>25.87843379999999</v>
+        <v>25.72566839999999</v>
       </c>
       <c r="O55">
-        <v>6.857784956999998</v>
+        <v>6.817302125999999</v>
       </c>
       <c r="P55">
-        <v>19.020648843</v>
+        <v>18.908366274</v>
       </c>
       <c r="Q55">
-        <v>25.920648843</v>
+        <v>25.808366274</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1233879034416026</v>
+        <v>0.1248301927342703</v>
       </c>
       <c r="T55">
-        <v>1.791868439759875</v>
+        <v>1.825177661299546</v>
       </c>
       <c r="U55">
         <v>0.0578</v>
@@ -6326,7 +6326,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.196223332305983</v>
+        <v>4.118515492818835</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6334,22 +6334,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08036270865776435</v>
+        <v>0.08021711269797549</v>
       </c>
       <c r="C56">
-        <v>108.3357106085415</v>
+        <v>106.4996943255876</v>
       </c>
       <c r="D56">
-        <v>244.4877106085415</v>
+        <v>245.2946943255876</v>
       </c>
       <c r="E56">
-        <v>-41.27799999999999</v>
+        <v>-38.63499999999999</v>
       </c>
       <c r="F56">
-        <v>142.722</v>
+        <v>145.365</v>
       </c>
       <c r="G56">
         <v>6.57</v>
@@ -6370,28 +6370,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M56">
-        <v>8.249331600000001</v>
+        <v>8.402097000000001</v>
       </c>
       <c r="N56">
-        <v>25.72566839999999</v>
+        <v>25.57290299999999</v>
       </c>
       <c r="O56">
-        <v>6.817302125999999</v>
+        <v>6.776819294999998</v>
       </c>
       <c r="P56">
-        <v>18.908366274</v>
+        <v>18.79608370499999</v>
       </c>
       <c r="Q56">
-        <v>25.808366274</v>
+        <v>25.696083705</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1248301927342703</v>
+        <v>0.1263365837732789</v>
       </c>
       <c r="T56">
-        <v>1.825177661299546</v>
+        <v>1.859967292685424</v>
       </c>
       <c r="U56">
         <v>0.0578</v>
@@ -6408,7 +6408,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.118515492818835</v>
+        <v>4.043633392949402</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6416,22 +6416,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08021711269797549</v>
+        <v>0.08151211673818662</v>
       </c>
       <c r="C57">
-        <v>106.4996943255876</v>
+        <v>96.86067242209222</v>
       </c>
       <c r="D57">
-        <v>245.2946943255876</v>
+        <v>238.2986724220922</v>
       </c>
       <c r="E57">
-        <v>-38.63499999999999</v>
+        <v>-35.99199999999999</v>
       </c>
       <c r="F57">
-        <v>145.365</v>
+        <v>148.008</v>
       </c>
       <c r="G57">
         <v>6.57</v>
@@ -6452,45 +6452,45 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M57">
-        <v>8.402097000000001</v>
+        <v>9.0728904</v>
       </c>
       <c r="N57">
-        <v>25.57290299999999</v>
+        <v>24.9021096</v>
       </c>
       <c r="O57">
-        <v>6.776819294999998</v>
+        <v>6.599059043999999</v>
       </c>
       <c r="P57">
-        <v>18.79608370499999</v>
+        <v>18.303050556</v>
       </c>
       <c r="Q57">
-        <v>25.696083705</v>
+        <v>25.203050556</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1263365837732789</v>
+        <v>0.1279114471322423</v>
       </c>
       <c r="T57">
-        <v>1.859967292685424</v>
+        <v>1.896338270952479</v>
       </c>
       <c r="U57">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V57">
         <v>0.265</v>
       </c>
       <c r="W57">
-        <v>0.042483</v>
+        <v>0.0450555</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y57">
-        <v>4.043633392949402</v>
+        <v>3.744672149902747</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6498,22 +6498,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08151211673818662</v>
+        <v>0.08139224577839776</v>
       </c>
       <c r="C58">
-        <v>96.86067242209222</v>
+        <v>94.84844898271527</v>
       </c>
       <c r="D58">
-        <v>238.2986724220922</v>
+        <v>238.9294489827153</v>
       </c>
       <c r="E58">
-        <v>-35.99199999999999</v>
+        <v>-33.34899999999999</v>
       </c>
       <c r="F58">
-        <v>148.008</v>
+        <v>150.651</v>
       </c>
       <c r="G58">
         <v>6.57</v>
@@ -6534,28 +6534,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M58">
-        <v>9.0728904</v>
+        <v>9.2349063</v>
       </c>
       <c r="N58">
-        <v>24.9021096</v>
+        <v>24.7400937</v>
       </c>
       <c r="O58">
-        <v>6.599059043999999</v>
+        <v>6.556124830499999</v>
       </c>
       <c r="P58">
-        <v>18.303050556</v>
+        <v>18.1839688695</v>
       </c>
       <c r="Q58">
-        <v>25.203050556</v>
+        <v>25.0839688695</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1279114471322423</v>
+        <v>0.1295595599497623</v>
       </c>
       <c r="T58">
-        <v>1.896338270952479</v>
+        <v>1.934400922627304</v>
       </c>
       <c r="U58">
         <v>0.0613</v>
@@ -6572,7 +6572,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.744672149902747</v>
+        <v>3.678976147272874</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6580,22 +6580,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08139224577839776</v>
+        <v>0.08127237481860891</v>
       </c>
       <c r="C59">
-        <v>94.84844898271527</v>
+        <v>92.83957373698462</v>
       </c>
       <c r="D59">
-        <v>238.9294489827153</v>
+        <v>239.5635737369847</v>
       </c>
       <c r="E59">
-        <v>-33.34899999999999</v>
+        <v>-30.70599999999996</v>
       </c>
       <c r="F59">
-        <v>150.651</v>
+        <v>153.294</v>
       </c>
       <c r="G59">
         <v>6.57</v>
@@ -6616,28 +6616,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M59">
-        <v>9.2349063</v>
+        <v>9.396922200000002</v>
       </c>
       <c r="N59">
-        <v>24.7400937</v>
+        <v>24.57807779999999</v>
       </c>
       <c r="O59">
-        <v>6.556124830499999</v>
+        <v>6.513190616999998</v>
       </c>
       <c r="P59">
-        <v>18.1839688695</v>
+        <v>18.06488718299999</v>
       </c>
       <c r="Q59">
-        <v>25.0839688695</v>
+        <v>24.96488718299999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1295595599497623</v>
+        <v>0.1312861543300212</v>
       </c>
       <c r="T59">
-        <v>1.934400922627304</v>
+        <v>1.97427608152474</v>
       </c>
       <c r="U59">
         <v>0.0613</v>
@@ -6654,7 +6654,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.678976147272874</v>
+        <v>3.615545524044031</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6662,22 +6662,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.0812723748186089</v>
+        <v>0.08115250385882004</v>
       </c>
       <c r="C60">
-        <v>92.83957373698476</v>
+        <v>90.83407341441117</v>
       </c>
       <c r="D60">
-        <v>239.5635737369848</v>
+        <v>240.2010734144112</v>
       </c>
       <c r="E60">
-        <v>-30.70600000000002</v>
+        <v>-28.06299999999999</v>
       </c>
       <c r="F60">
-        <v>153.294</v>
+        <v>155.937</v>
       </c>
       <c r="G60">
         <v>6.57</v>
@@ -6698,28 +6698,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M60">
-        <v>9.396922199999999</v>
+        <v>9.558938100000001</v>
       </c>
       <c r="N60">
-        <v>24.5780778</v>
+        <v>24.4160619</v>
       </c>
       <c r="O60">
-        <v>6.513190616999999</v>
+        <v>6.470256403499999</v>
       </c>
       <c r="P60">
-        <v>18.064887183</v>
+        <v>17.9458054965</v>
       </c>
       <c r="Q60">
-        <v>24.964887183</v>
+        <v>24.8458054965</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1312861543300212</v>
+        <v>0.1330969728263904</v>
       </c>
       <c r="T60">
-        <v>1.974276081524739</v>
+        <v>2.016096370124489</v>
       </c>
       <c r="U60">
         <v>0.0613</v>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.615545524044032</v>
+        <v>3.554265091433116</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6744,22 +6744,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08115250385882004</v>
+        <v>0.08226743289903118</v>
       </c>
       <c r="C61">
-        <v>90.83407341441117</v>
+        <v>82.38945672354379</v>
       </c>
       <c r="D61">
-        <v>240.2010734144112</v>
+        <v>234.3994567235438</v>
       </c>
       <c r="E61">
-        <v>-28.06299999999999</v>
+        <v>-25.41999999999999</v>
       </c>
       <c r="F61">
-        <v>155.937</v>
+        <v>158.58</v>
       </c>
       <c r="G61">
         <v>6.57</v>
@@ -6780,45 +6780,45 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M61">
-        <v>9.558938100000001</v>
+        <v>10.164978</v>
       </c>
       <c r="N61">
-        <v>24.4160619</v>
+        <v>23.81002199999999</v>
       </c>
       <c r="O61">
-        <v>6.470256403499999</v>
+        <v>6.309655829999999</v>
       </c>
       <c r="P61">
-        <v>17.9458054965</v>
+        <v>17.50036616999999</v>
       </c>
       <c r="Q61">
-        <v>24.8458054965</v>
+        <v>24.40036616999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1330969728263904</v>
+        <v>0.134998332247578</v>
       </c>
       <c r="T61">
-        <v>2.016096370124489</v>
+        <v>2.060007673154225</v>
       </c>
       <c r="U61">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V61">
         <v>0.265</v>
       </c>
       <c r="W61">
-        <v>0.0450555</v>
+        <v>0.0471135</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y61">
-        <v>3.554265091433116</v>
+        <v>3.342358438945956</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6826,22 +6826,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08226743289903118</v>
+        <v>0.08216814193924232</v>
       </c>
       <c r="C62">
-        <v>82.38945672354379</v>
+        <v>80.25173233384271</v>
       </c>
       <c r="D62">
-        <v>234.3994567235438</v>
+        <v>234.9047323338427</v>
       </c>
       <c r="E62">
-        <v>-25.41999999999999</v>
+        <v>-22.77699999999999</v>
       </c>
       <c r="F62">
-        <v>158.58</v>
+        <v>161.223</v>
       </c>
       <c r="G62">
         <v>6.57</v>
@@ -6862,28 +6862,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M62">
-        <v>10.164978</v>
+        <v>10.3343943</v>
       </c>
       <c r="N62">
-        <v>23.81002199999999</v>
+        <v>23.64060569999999</v>
       </c>
       <c r="O62">
-        <v>6.309655829999999</v>
+        <v>6.264760510499999</v>
       </c>
       <c r="P62">
-        <v>17.50036616999999</v>
+        <v>17.3758451895</v>
       </c>
       <c r="Q62">
-        <v>24.40036616999999</v>
+        <v>24.2758451895</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.134998332247578</v>
+        <v>0.1369971972801085</v>
       </c>
       <c r="T62">
-        <v>2.060007673154225</v>
+        <v>2.106170837877795</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6900,7 +6900,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.342358438945956</v>
+        <v>3.28756567765176</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6908,22 +6908,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08216814193924232</v>
+        <v>0.08206885097945346</v>
       </c>
       <c r="C63">
-        <v>80.25173233384271</v>
+        <v>78.11619101206702</v>
       </c>
       <c r="D63">
-        <v>234.9047323338427</v>
+        <v>235.412191012067</v>
       </c>
       <c r="E63">
-        <v>-22.77699999999999</v>
+        <v>-20.13399999999999</v>
       </c>
       <c r="F63">
-        <v>161.223</v>
+        <v>163.866</v>
       </c>
       <c r="G63">
         <v>6.57</v>
@@ -6944,28 +6944,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M63">
-        <v>10.3343943</v>
+        <v>10.5038106</v>
       </c>
       <c r="N63">
-        <v>23.64060569999999</v>
+        <v>23.47118939999999</v>
       </c>
       <c r="O63">
-        <v>6.264760510499999</v>
+        <v>6.219865190999998</v>
       </c>
       <c r="P63">
-        <v>17.3758451895</v>
+        <v>17.251324209</v>
       </c>
       <c r="Q63">
-        <v>24.2758451895</v>
+        <v>24.151324209</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1369971972801085</v>
+        <v>0.1391012657354039</v>
       </c>
       <c r="T63">
-        <v>2.106170837877795</v>
+        <v>2.154763642849973</v>
       </c>
       <c r="U63">
         <v>0.0641</v>
@@ -6982,7 +6982,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.28756567765176</v>
+        <v>3.23454042478641</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6990,22 +6990,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08206885097945346</v>
+        <v>0.0819695600196646</v>
       </c>
       <c r="C64">
-        <v>78.11619101206702</v>
+        <v>75.98284693692386</v>
       </c>
       <c r="D64">
-        <v>235.412191012067</v>
+        <v>235.9218469369239</v>
       </c>
       <c r="E64">
-        <v>-20.13399999999999</v>
+        <v>-17.49099999999999</v>
       </c>
       <c r="F64">
-        <v>163.866</v>
+        <v>166.509</v>
       </c>
       <c r="G64">
         <v>6.57</v>
@@ -7026,28 +7026,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M64">
-        <v>10.5038106</v>
+        <v>10.6732269</v>
       </c>
       <c r="N64">
-        <v>23.47118939999999</v>
+        <v>23.30177309999999</v>
       </c>
       <c r="O64">
-        <v>6.219865190999998</v>
+        <v>6.174969871499998</v>
       </c>
       <c r="P64">
-        <v>17.251324209</v>
+        <v>17.12680322849999</v>
       </c>
       <c r="Q64">
-        <v>24.151324209</v>
+        <v>24.0268032285</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1391012657354039</v>
+        <v>0.1413190676207151</v>
       </c>
       <c r="T64">
-        <v>2.154763642849973</v>
+        <v>2.205983085928756</v>
       </c>
       <c r="U64">
         <v>0.0641</v>
@@ -7064,7 +7064,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.23454042478641</v>
+        <v>3.183198513281863</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -7072,22 +7072,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.0819695600196646</v>
+        <v>0.08187026905987574</v>
       </c>
       <c r="C65">
-        <v>75.98284693692386</v>
+        <v>73.85171441017158</v>
       </c>
       <c r="D65">
-        <v>235.9218469369239</v>
+        <v>236.4337144101716</v>
       </c>
       <c r="E65">
-        <v>-17.49099999999999</v>
+        <v>-14.84799999999998</v>
       </c>
       <c r="F65">
-        <v>166.509</v>
+        <v>169.152</v>
       </c>
       <c r="G65">
         <v>6.57</v>
@@ -7108,28 +7108,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M65">
-        <v>10.6732269</v>
+        <v>10.8426432</v>
       </c>
       <c r="N65">
-        <v>23.30177309999999</v>
+        <v>23.13235679999999</v>
       </c>
       <c r="O65">
-        <v>6.174969871499998</v>
+        <v>6.130074551999998</v>
       </c>
       <c r="P65">
-        <v>17.12680322849999</v>
+        <v>17.00228224799999</v>
       </c>
       <c r="Q65">
-        <v>24.0268032285</v>
+        <v>23.902282248</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1413190676207151</v>
+        <v>0.143660080721877</v>
       </c>
       <c r="T65">
-        <v>2.205983085928756</v>
+        <v>2.260048053623026</v>
       </c>
       <c r="U65">
         <v>0.0641</v>
@@ -7146,7 +7146,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.183198513281863</v>
+        <v>3.133461036511834</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -7154,22 +7154,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08187026905987574</v>
+        <v>0.08177097810008688</v>
       </c>
       <c r="C66">
-        <v>73.85171441017158</v>
+        <v>71.72280785795755</v>
       </c>
       <c r="D66">
-        <v>236.4337144101716</v>
+        <v>236.9478078579576</v>
       </c>
       <c r="E66">
-        <v>-14.84799999999998</v>
+        <v>-12.20499999999998</v>
       </c>
       <c r="F66">
-        <v>169.152</v>
+        <v>171.795</v>
       </c>
       <c r="G66">
         <v>6.57</v>
@@ -7190,28 +7190,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M66">
-        <v>10.8426432</v>
+        <v>11.0120595</v>
       </c>
       <c r="N66">
-        <v>23.13235679999999</v>
+        <v>22.96294049999999</v>
       </c>
       <c r="O66">
-        <v>6.130074551999998</v>
+        <v>6.085179232499999</v>
       </c>
       <c r="P66">
-        <v>17.00228224799999</v>
+        <v>16.8777612675</v>
       </c>
       <c r="Q66">
-        <v>23.902282248</v>
+        <v>23.7777612675</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.143660080721877</v>
+        <v>0.1461348660002482</v>
       </c>
       <c r="T66">
-        <v>2.260048053623026</v>
+        <v>2.317202448042684</v>
       </c>
       <c r="U66">
         <v>0.0641</v>
@@ -7228,7 +7228,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.133461036511834</v>
+        <v>3.085253943642421</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7236,22 +7236,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08177097810008688</v>
+        <v>0.08167168714029802</v>
       </c>
       <c r="C67">
-        <v>71.72280785795755</v>
+        <v>69.59614183217346</v>
       </c>
       <c r="D67">
-        <v>236.9478078579576</v>
+        <v>237.4641418321735</v>
       </c>
       <c r="E67">
-        <v>-12.20499999999998</v>
+        <v>-9.561999999999983</v>
       </c>
       <c r="F67">
-        <v>171.795</v>
+        <v>174.438</v>
       </c>
       <c r="G67">
         <v>6.57</v>
@@ -7272,28 +7272,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M67">
-        <v>11.0120595</v>
+        <v>11.1814758</v>
       </c>
       <c r="N67">
-        <v>22.96294049999999</v>
+        <v>22.79352419999999</v>
       </c>
       <c r="O67">
-        <v>6.085179232499999</v>
+        <v>6.040283912999999</v>
       </c>
       <c r="P67">
-        <v>16.8777612675</v>
+        <v>16.75324028699999</v>
       </c>
       <c r="Q67">
-        <v>23.7777612675</v>
+        <v>23.653240287</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1461348660002482</v>
+        <v>0.1487552268832295</v>
       </c>
       <c r="T67">
-        <v>2.317202448042684</v>
+        <v>2.377718865663498</v>
       </c>
       <c r="U67">
         <v>0.0641</v>
@@ -7310,7 +7310,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.085253943642421</v>
+        <v>3.038507671769051</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7318,22 +7318,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08167168714029802</v>
+        <v>0.08541350618050915</v>
       </c>
       <c r="C68">
-        <v>69.59614183217346</v>
+        <v>48.93236405992289</v>
       </c>
       <c r="D68">
-        <v>237.4641418321735</v>
+        <v>219.4433640599229</v>
       </c>
       <c r="E68">
-        <v>-9.561999999999983</v>
+        <v>-6.918999999999983</v>
       </c>
       <c r="F68">
-        <v>174.438</v>
+        <v>177.081</v>
       </c>
       <c r="G68">
         <v>6.57</v>
@@ -7354,45 +7354,45 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M68">
-        <v>11.1814758</v>
+        <v>12.7321239</v>
       </c>
       <c r="N68">
-        <v>22.79352419999999</v>
+        <v>21.24287609999999</v>
       </c>
       <c r="O68">
-        <v>6.040283912999999</v>
+        <v>5.629362166499997</v>
       </c>
       <c r="P68">
-        <v>16.75324028699999</v>
+        <v>15.61351393349999</v>
       </c>
       <c r="Q68">
-        <v>23.653240287</v>
+        <v>22.51351393349999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1487552268832295</v>
+        <v>0.1515343975166944</v>
       </c>
       <c r="T68">
-        <v>2.377718865663498</v>
+        <v>2.4419029449583</v>
       </c>
       <c r="U68">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V68">
         <v>0.265</v>
       </c>
       <c r="W68">
-        <v>0.0471135</v>
+        <v>0.0528465</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y68">
-        <v>3.038507671769051</v>
+        <v>2.668447170860471</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7400,22 +7400,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08541350618050915</v>
+        <v>0.0853715452207203</v>
       </c>
       <c r="C69">
-        <v>48.93236405992289</v>
+        <v>46.47627310862447</v>
       </c>
       <c r="D69">
-        <v>219.4433640599229</v>
+        <v>219.6302731086245</v>
       </c>
       <c r="E69">
-        <v>-6.918999999999983</v>
+        <v>-4.275999999999982</v>
       </c>
       <c r="F69">
-        <v>177.081</v>
+        <v>179.724</v>
       </c>
       <c r="G69">
         <v>6.57</v>
@@ -7436,28 +7436,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M69">
-        <v>12.7321239</v>
+        <v>12.9221556</v>
       </c>
       <c r="N69">
-        <v>21.24287609999999</v>
+        <v>21.05284439999999</v>
       </c>
       <c r="O69">
-        <v>5.629362166499997</v>
+        <v>5.579003765999998</v>
       </c>
       <c r="P69">
-        <v>15.61351393349999</v>
+        <v>15.47384063399999</v>
       </c>
       <c r="Q69">
-        <v>22.51351393349999</v>
+        <v>22.373840634</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1515343975166944</v>
+        <v>0.1544872663147509</v>
       </c>
       <c r="T69">
-        <v>2.4419029449583</v>
+        <v>2.510098529209028</v>
       </c>
       <c r="U69">
         <v>0.07190000000000001</v>
@@ -7474,7 +7474,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.668447170860471</v>
+        <v>2.629205300700758</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7482,22 +7482,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.0853715452207203</v>
+        <v>0.08532958426093143</v>
       </c>
       <c r="C70">
-        <v>46.47627310862447</v>
+        <v>44.0205008251846</v>
       </c>
       <c r="D70">
-        <v>219.6302731086245</v>
+        <v>219.8175008251846</v>
       </c>
       <c r="E70">
-        <v>-4.275999999999982</v>
+        <v>-1.632999999999981</v>
       </c>
       <c r="F70">
-        <v>179.724</v>
+        <v>182.367</v>
       </c>
       <c r="G70">
         <v>6.57</v>
@@ -7518,28 +7518,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M70">
-        <v>12.9221556</v>
+        <v>13.1121873</v>
       </c>
       <c r="N70">
-        <v>21.05284439999999</v>
+        <v>20.86281269999999</v>
       </c>
       <c r="O70">
-        <v>5.579003765999998</v>
+        <v>5.528645365499998</v>
       </c>
       <c r="P70">
-        <v>15.47384063399999</v>
+        <v>15.33416733449999</v>
       </c>
       <c r="Q70">
-        <v>22.373840634</v>
+        <v>22.2341673345</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1544872663147509</v>
+        <v>0.1576306427771982</v>
       </c>
       <c r="T70">
-        <v>2.510098529209028</v>
+        <v>2.582693828572706</v>
       </c>
       <c r="U70">
         <v>0.07190000000000001</v>
@@ -7556,7 +7556,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.629205300700758</v>
+        <v>2.591100876052921</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7564,22 +7564,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08532958426093143</v>
+        <v>0.08528762330114256</v>
       </c>
       <c r="C71">
-        <v>44.0205008251846</v>
+        <v>41.56504802526069</v>
       </c>
       <c r="D71">
-        <v>219.8175008251846</v>
+        <v>220.0050480252607</v>
       </c>
       <c r="E71">
-        <v>-1.632999999999981</v>
+        <v>1.010000000000019</v>
       </c>
       <c r="F71">
-        <v>182.367</v>
+        <v>185.01</v>
       </c>
       <c r="G71">
         <v>6.57</v>
@@ -7600,28 +7600,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M71">
-        <v>13.1121873</v>
+        <v>13.302219</v>
       </c>
       <c r="N71">
-        <v>20.86281269999999</v>
+        <v>20.67278099999999</v>
       </c>
       <c r="O71">
-        <v>5.528645365499998</v>
+        <v>5.478286964999999</v>
       </c>
       <c r="P71">
-        <v>15.33416733449999</v>
+        <v>15.19449403499999</v>
       </c>
       <c r="Q71">
-        <v>22.2341673345</v>
+        <v>22.094494035</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1576306427771982</v>
+        <v>0.1609835776704752</v>
       </c>
       <c r="T71">
-        <v>2.582693828572706</v>
+        <v>2.660128814560629</v>
       </c>
       <c r="U71">
         <v>0.07190000000000001</v>
@@ -7638,7 +7638,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.591100876052921</v>
+        <v>2.554085149252165</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7646,22 +7646,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08528762330114256</v>
+        <v>0.0852456623413537</v>
       </c>
       <c r="C72">
-        <v>41.56504802526069</v>
+        <v>39.10991552729632</v>
       </c>
       <c r="D72">
-        <v>220.0050480252607</v>
+        <v>220.1929155272963</v>
       </c>
       <c r="E72">
-        <v>1.010000000000019</v>
+        <v>3.65300000000002</v>
       </c>
       <c r="F72">
-        <v>185.01</v>
+        <v>187.653</v>
       </c>
       <c r="G72">
         <v>6.57</v>
@@ -7682,28 +7682,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M72">
-        <v>13.302219</v>
+        <v>13.4922507</v>
       </c>
       <c r="N72">
-        <v>20.67278099999999</v>
+        <v>20.48274929999999</v>
       </c>
       <c r="O72">
-        <v>5.478286964999999</v>
+        <v>5.427928564499997</v>
       </c>
       <c r="P72">
-        <v>15.19449403499999</v>
+        <v>15.05482073549999</v>
       </c>
       <c r="Q72">
-        <v>22.094494035</v>
+        <v>21.9548207355</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1609835776704752</v>
+        <v>0.1645677494529438</v>
       </c>
       <c r="T72">
-        <v>2.660128814560629</v>
+        <v>2.742904144409788</v>
       </c>
       <c r="U72">
         <v>0.07190000000000001</v>
@@ -7720,7 +7720,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.554085149252165</v>
+        <v>2.518112118981008</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7728,22 +7728,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08524566234135371</v>
+        <v>0.08726758138156485</v>
       </c>
       <c r="C73">
-        <v>39.10991552729627</v>
+        <v>27.76472303710287</v>
       </c>
       <c r="D73">
-        <v>220.1929155272963</v>
+        <v>211.4907230371029</v>
       </c>
       <c r="E73">
-        <v>3.652999999999992</v>
+        <v>6.295999999999992</v>
       </c>
       <c r="F73">
-        <v>187.653</v>
+        <v>190.296</v>
       </c>
       <c r="G73">
         <v>6.57</v>
@@ -7764,45 +7764,45 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M73">
-        <v>13.4922507</v>
+        <v>14.4244368</v>
       </c>
       <c r="N73">
-        <v>20.48274929999999</v>
+        <v>19.55056319999999</v>
       </c>
       <c r="O73">
-        <v>5.427928564499999</v>
+        <v>5.180899247999998</v>
       </c>
       <c r="P73">
-        <v>15.05482073549999</v>
+        <v>14.36966395199999</v>
       </c>
       <c r="Q73">
-        <v>21.9548207355</v>
+        <v>21.26966395199999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1645677494529438</v>
+        <v>0.1684079335055887</v>
       </c>
       <c r="T73">
-        <v>2.742904144409787</v>
+        <v>2.831591997819601</v>
       </c>
       <c r="U73">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V73">
         <v>0.265</v>
       </c>
       <c r="W73">
-        <v>0.0528465</v>
+        <v>0.05571300000000001</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y73">
-        <v>2.518112118981009</v>
+        <v>2.355377923663542</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7810,22 +7810,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08726758138156485</v>
+        <v>0.08725428542177599</v>
       </c>
       <c r="C74">
-        <v>27.76472303710287</v>
+        <v>25.17670059922094</v>
       </c>
       <c r="D74">
-        <v>211.4907230371029</v>
+        <v>211.5457005992209</v>
       </c>
       <c r="E74">
-        <v>6.295999999999992</v>
+        <v>8.938999999999993</v>
       </c>
       <c r="F74">
-        <v>190.296</v>
+        <v>192.939</v>
       </c>
       <c r="G74">
         <v>6.57</v>
@@ -7846,28 +7846,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M74">
-        <v>14.4244368</v>
+        <v>14.6247762</v>
       </c>
       <c r="N74">
-        <v>19.55056319999999</v>
+        <v>19.35022379999999</v>
       </c>
       <c r="O74">
-        <v>5.180899247999998</v>
+        <v>5.127809306999999</v>
       </c>
       <c r="P74">
-        <v>14.36966395199999</v>
+        <v>14.222414493</v>
       </c>
       <c r="Q74">
-        <v>21.26966395199999</v>
+        <v>21.122414493</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1684079335055887</v>
+        <v>0.1725325756362073</v>
       </c>
       <c r="T74">
-        <v>2.831591997819601</v>
+        <v>2.926849321852363</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7884,7 +7884,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.355377923663542</v>
+        <v>2.323112472654453</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7892,22 +7892,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08725428542177599</v>
+        <v>0.08724098946198713</v>
       </c>
       <c r="C75">
-        <v>25.17670059922094</v>
+        <v>22.58870675189101</v>
       </c>
       <c r="D75">
-        <v>211.5457005992209</v>
+        <v>211.600706751891</v>
       </c>
       <c r="E75">
-        <v>8.938999999999993</v>
+        <v>11.58199999999999</v>
       </c>
       <c r="F75">
-        <v>192.939</v>
+        <v>195.582</v>
       </c>
       <c r="G75">
         <v>6.57</v>
@@ -7928,28 +7928,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M75">
-        <v>14.6247762</v>
+        <v>14.8251156</v>
       </c>
       <c r="N75">
-        <v>19.35022379999999</v>
+        <v>19.14988439999999</v>
       </c>
       <c r="O75">
-        <v>5.127809306999999</v>
+        <v>5.074719365999998</v>
       </c>
       <c r="P75">
-        <v>14.222414493</v>
+        <v>14.075165034</v>
       </c>
       <c r="Q75">
-        <v>21.122414493</v>
+        <v>20.975165034</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1725325756362073</v>
+        <v>0.1769744979307197</v>
       </c>
       <c r="T75">
-        <v>2.926849321852363</v>
+        <v>3.029434132349184</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7966,7 +7966,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.323112472654453</v>
+        <v>2.291719060861825</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7974,22 +7974,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08724098946198713</v>
+        <v>0.08722769350219825</v>
       </c>
       <c r="C76">
-        <v>22.58870675189101</v>
+        <v>20.00074151742135</v>
       </c>
       <c r="D76">
-        <v>211.600706751891</v>
+        <v>211.6557415174214</v>
       </c>
       <c r="E76">
-        <v>11.58199999999999</v>
+        <v>14.22500000000002</v>
       </c>
       <c r="F76">
-        <v>195.582</v>
+        <v>198.225</v>
       </c>
       <c r="G76">
         <v>6.57</v>
@@ -8010,28 +8010,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M76">
-        <v>14.8251156</v>
+        <v>15.025455</v>
       </c>
       <c r="N76">
-        <v>19.14988439999999</v>
+        <v>18.94954499999999</v>
       </c>
       <c r="O76">
-        <v>5.074719365999998</v>
+        <v>5.021629424999999</v>
       </c>
       <c r="P76">
-        <v>14.075165034</v>
+        <v>13.92791557499999</v>
       </c>
       <c r="Q76">
-        <v>20.975165034</v>
+        <v>20.827915575</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1769744979307197</v>
+        <v>0.181771774008793</v>
       </c>
       <c r="T76">
-        <v>3.029434132349184</v>
+        <v>3.140225727685751</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -8048,7 +8048,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.291719060861825</v>
+        <v>2.261162806717</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -8056,22 +8056,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08722769350219825</v>
+        <v>0.08721439754240939</v>
       </c>
       <c r="C77">
-        <v>20.00074151742135</v>
+        <v>17.41280491814308</v>
       </c>
       <c r="D77">
-        <v>211.6557415174214</v>
+        <v>211.7108049181431</v>
       </c>
       <c r="E77">
-        <v>14.22500000000002</v>
+        <v>16.86800000000002</v>
       </c>
       <c r="F77">
-        <v>198.225</v>
+        <v>200.868</v>
       </c>
       <c r="G77">
         <v>6.57</v>
@@ -8092,28 +8092,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M77">
-        <v>15.025455</v>
+        <v>15.2257944</v>
       </c>
       <c r="N77">
-        <v>18.94954499999999</v>
+        <v>18.74920559999999</v>
       </c>
       <c r="O77">
-        <v>5.021629424999999</v>
+        <v>4.968539483999997</v>
       </c>
       <c r="P77">
-        <v>13.92791557499999</v>
+        <v>13.78066611599999</v>
       </c>
       <c r="Q77">
-        <v>20.827915575</v>
+        <v>20.68066611599999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.181771774008793</v>
+        <v>0.1869688230933725</v>
       </c>
       <c r="T77">
-        <v>3.140225727685751</v>
+        <v>3.260249955967032</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -8130,7 +8130,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.261162806717</v>
+        <v>2.231410664523356</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -8138,22 +8138,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08721439754240939</v>
+        <v>0.08720110158262054</v>
       </c>
       <c r="C78">
-        <v>17.41280491814308</v>
+        <v>14.824896976411</v>
       </c>
       <c r="D78">
-        <v>211.7108049181431</v>
+        <v>211.765896976411</v>
       </c>
       <c r="E78">
-        <v>16.86800000000002</v>
+        <v>19.51100000000002</v>
       </c>
       <c r="F78">
-        <v>200.868</v>
+        <v>203.511</v>
       </c>
       <c r="G78">
         <v>6.57</v>
@@ -8174,28 +8174,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M78">
-        <v>15.2257944</v>
+        <v>15.4261338</v>
       </c>
       <c r="N78">
-        <v>18.74920559999999</v>
+        <v>18.54886619999999</v>
       </c>
       <c r="O78">
-        <v>4.968539483999997</v>
+        <v>4.915449542999998</v>
       </c>
       <c r="P78">
-        <v>13.78066611599999</v>
+        <v>13.63341665699999</v>
       </c>
       <c r="Q78">
-        <v>20.68066611599999</v>
+        <v>20.533416657</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1869688230933725</v>
+        <v>0.1926177894896545</v>
       </c>
       <c r="T78">
-        <v>3.260249955967032</v>
+        <v>3.390711073664076</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -8212,7 +8212,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.231410664523356</v>
+        <v>2.202431305243832</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -8220,22 +8220,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08720110158262054</v>
+        <v>0.08718780562283167</v>
       </c>
       <c r="C79">
-        <v>14.824896976411</v>
+        <v>12.23701771460298</v>
       </c>
       <c r="D79">
-        <v>211.765896976411</v>
+        <v>211.821017714603</v>
       </c>
       <c r="E79">
-        <v>19.51100000000002</v>
+        <v>22.15400000000002</v>
       </c>
       <c r="F79">
-        <v>203.511</v>
+        <v>206.154</v>
       </c>
       <c r="G79">
         <v>6.57</v>
@@ -8256,28 +8256,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M79">
-        <v>15.4261338</v>
+        <v>15.6264732</v>
       </c>
       <c r="N79">
-        <v>18.54886619999999</v>
+        <v>18.34852679999999</v>
       </c>
       <c r="O79">
-        <v>4.915449542999998</v>
+        <v>4.862359601999998</v>
       </c>
       <c r="P79">
-        <v>13.63341665699999</v>
+        <v>13.48616719799999</v>
       </c>
       <c r="Q79">
-        <v>20.533416657</v>
+        <v>20.386167198</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1926177894896545</v>
+        <v>0.1987802982855985</v>
       </c>
       <c r="T79">
-        <v>3.390711073664076</v>
+        <v>3.533032292969942</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -8294,7 +8294,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.202431305243832</v>
+        <v>2.174195006458654</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8302,22 +8302,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08718780562283167</v>
+        <v>0.08717450966304283</v>
       </c>
       <c r="C80">
-        <v>12.23701771460298</v>
+        <v>9.649167155120097</v>
       </c>
       <c r="D80">
-        <v>211.821017714603</v>
+        <v>211.8761671551201</v>
       </c>
       <c r="E80">
-        <v>22.15400000000002</v>
+        <v>24.79700000000003</v>
       </c>
       <c r="F80">
-        <v>206.154</v>
+        <v>208.797</v>
       </c>
       <c r="G80">
         <v>6.57</v>
@@ -8338,28 +8338,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M80">
-        <v>15.6264732</v>
+        <v>15.8268126</v>
       </c>
       <c r="N80">
-        <v>18.34852679999999</v>
+        <v>18.14818739999999</v>
       </c>
       <c r="O80">
-        <v>4.862359601999998</v>
+        <v>4.809269660999997</v>
       </c>
       <c r="P80">
-        <v>13.48616719799999</v>
+        <v>13.33891773899999</v>
       </c>
       <c r="Q80">
-        <v>20.386167198</v>
+        <v>20.23891773899999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1987802982855985</v>
+        <v>0.2055297126811563</v>
       </c>
       <c r="T80">
-        <v>3.533032292969942</v>
+        <v>3.688907914114464</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -8376,7 +8376,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.174195006458654</v>
+        <v>2.146673550680696</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8384,22 +8384,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08717450966304283</v>
+        <v>0.08716121370325396</v>
       </c>
       <c r="C81">
-        <v>9.649167155120097</v>
+        <v>7.061345320387147</v>
       </c>
       <c r="D81">
-        <v>211.8761671551201</v>
+        <v>211.9313453203872</v>
       </c>
       <c r="E81">
-        <v>24.79700000000003</v>
+        <v>27.44000000000003</v>
       </c>
       <c r="F81">
-        <v>208.797</v>
+        <v>211.44</v>
       </c>
       <c r="G81">
         <v>6.57</v>
@@ -8420,28 +8420,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M81">
-        <v>15.8268126</v>
+        <v>16.027152</v>
       </c>
       <c r="N81">
-        <v>18.14818739999999</v>
+        <v>17.94784799999999</v>
       </c>
       <c r="O81">
-        <v>4.809269660999997</v>
+        <v>4.756179719999998</v>
       </c>
       <c r="P81">
-        <v>13.33891773899999</v>
+        <v>13.19166827999999</v>
       </c>
       <c r="Q81">
-        <v>20.23891773899999</v>
+        <v>20.09166827999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2055297126811563</v>
+        <v>0.2129540685162698</v>
       </c>
       <c r="T81">
-        <v>3.688907914114464</v>
+        <v>3.860371097373436</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -8458,7 +8458,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.146673550680696</v>
+        <v>2.119840131297188</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8466,22 +8466,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08716121370325396</v>
+        <v>0.08714791774346509</v>
       </c>
       <c r="C82">
-        <v>7.061345320387147</v>
+        <v>4.473552232851858</v>
       </c>
       <c r="D82">
-        <v>211.9313453203872</v>
+        <v>211.9865522328519</v>
       </c>
       <c r="E82">
-        <v>27.44000000000003</v>
+        <v>30.08300000000003</v>
       </c>
       <c r="F82">
-        <v>211.44</v>
+        <v>214.083</v>
       </c>
       <c r="G82">
         <v>6.57</v>
@@ -8502,28 +8502,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M82">
-        <v>16.027152</v>
+        <v>16.2274914</v>
       </c>
       <c r="N82">
-        <v>17.94784799999999</v>
+        <v>17.74750859999999</v>
       </c>
       <c r="O82">
-        <v>4.756179719999998</v>
+        <v>4.703089778999998</v>
       </c>
       <c r="P82">
-        <v>13.19166827999999</v>
+        <v>13.04441882099999</v>
       </c>
       <c r="Q82">
-        <v>20.09166827999999</v>
+        <v>19.944418821</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2129540685162698</v>
+        <v>0.2211599354919215</v>
       </c>
       <c r="T82">
-        <v>3.860371097373436</v>
+        <v>4.049883036764931</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8540,7 +8540,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.119840131297188</v>
+        <v>2.093669265478704</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8548,22 +8548,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08714791774346509</v>
+        <v>0.08713462178367623</v>
       </c>
       <c r="C83">
-        <v>4.473552232851858</v>
+        <v>1.885787914985514</v>
       </c>
       <c r="D83">
-        <v>211.9865522328519</v>
+        <v>212.0417879149855</v>
       </c>
       <c r="E83">
-        <v>30.08300000000003</v>
+        <v>32.72600000000003</v>
       </c>
       <c r="F83">
-        <v>214.083</v>
+        <v>216.726</v>
       </c>
       <c r="G83">
         <v>6.57</v>
@@ -8584,28 +8584,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M83">
-        <v>16.2274914</v>
+        <v>16.4278308</v>
       </c>
       <c r="N83">
-        <v>17.74750859999999</v>
+        <v>17.54716919999999</v>
       </c>
       <c r="O83">
-        <v>4.703089778999998</v>
+        <v>4.649999837999998</v>
       </c>
       <c r="P83">
-        <v>13.04441882099999</v>
+        <v>12.89716936199999</v>
       </c>
       <c r="Q83">
-        <v>19.944418821</v>
+        <v>19.79716936199999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2211599354919215</v>
+        <v>0.230277565464868</v>
       </c>
       <c r="T83">
-        <v>4.049883036764931</v>
+        <v>4.260451858311039</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8622,7 +8622,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.093669265478704</v>
+        <v>2.068136713460671</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8630,22 +8630,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08713462178367623</v>
+        <v>0.08712132582388737</v>
       </c>
       <c r="C84">
-        <v>1.885787914985514</v>
+        <v>-0.7019476107171556</v>
       </c>
       <c r="D84">
-        <v>212.0417879149855</v>
+        <v>212.0970523892829</v>
       </c>
       <c r="E84">
-        <v>32.72600000000003</v>
+        <v>35.36900000000003</v>
       </c>
       <c r="F84">
-        <v>216.726</v>
+        <v>219.369</v>
       </c>
       <c r="G84">
         <v>6.57</v>
@@ -8666,28 +8666,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M84">
-        <v>16.4278308</v>
+        <v>16.6281702</v>
       </c>
       <c r="N84">
-        <v>17.54716919999999</v>
+        <v>17.34682979999999</v>
       </c>
       <c r="O84">
-        <v>4.649999837999998</v>
+        <v>4.596909896999998</v>
       </c>
       <c r="P84">
-        <v>12.89716936199999</v>
+        <v>12.74991990299999</v>
       </c>
       <c r="Q84">
-        <v>19.79716936199999</v>
+        <v>19.649919903</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.230277565464868</v>
+        <v>0.2404678577875728</v>
       </c>
       <c r="T84">
-        <v>4.260451858311039</v>
+        <v>4.495793482391981</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8704,7 +8704,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.068136713460671</v>
+        <v>2.04321940365994</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8712,22 +8712,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08712132582388737</v>
+        <v>0.0871080298640985</v>
       </c>
       <c r="C85">
-        <v>-0.7019476107171556</v>
+        <v>-3.289654321737828</v>
       </c>
       <c r="D85">
-        <v>212.0970523892829</v>
+        <v>212.1523456782622</v>
       </c>
       <c r="E85">
-        <v>35.36900000000003</v>
+        <v>38.01200000000003</v>
       </c>
       <c r="F85">
-        <v>219.369</v>
+        <v>222.012</v>
       </c>
       <c r="G85">
         <v>6.57</v>
@@ -8748,28 +8748,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M85">
-        <v>16.6281702</v>
+        <v>16.8285096</v>
       </c>
       <c r="N85">
-        <v>17.34682979999999</v>
+        <v>17.14649039999999</v>
       </c>
       <c r="O85">
-        <v>4.596909896999998</v>
+        <v>4.543819955999997</v>
       </c>
       <c r="P85">
-        <v>12.74991990299999</v>
+        <v>12.60267044399999</v>
       </c>
       <c r="Q85">
-        <v>19.649919903</v>
+        <v>19.502670444</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2404678577875728</v>
+        <v>0.2519319366506158</v>
       </c>
       <c r="T85">
-        <v>4.495793482391981</v>
+        <v>4.760552809483043</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8786,7 +8786,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.04321940365994</v>
+        <v>2.018895363140179</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8794,22 +8794,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.0871080298640985</v>
+        <v>0.09596618390430964</v>
       </c>
       <c r="C86">
-        <v>-3.2896543217378</v>
+        <v>-37.3274568467757</v>
       </c>
       <c r="D86">
-        <v>212.1523456782622</v>
+        <v>180.7575431532243</v>
       </c>
       <c r="E86">
-        <v>38.012</v>
+        <v>40.655</v>
       </c>
       <c r="F86">
-        <v>222.012</v>
+        <v>224.655</v>
       </c>
       <c r="G86">
         <v>6.57</v>
@@ -8830,45 +8830,45 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M86">
-        <v>16.8285096</v>
+        <v>20.21895</v>
       </c>
       <c r="N86">
-        <v>17.14649039999999</v>
+        <v>13.75604999999999</v>
       </c>
       <c r="O86">
-        <v>4.543819955999998</v>
+        <v>3.645353249999999</v>
       </c>
       <c r="P86">
-        <v>12.602670444</v>
+        <v>10.11069675</v>
       </c>
       <c r="Q86">
-        <v>19.502670444</v>
+        <v>17.01069675</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2519319366506156</v>
+        <v>0.2649245593620642</v>
       </c>
       <c r="T86">
-        <v>4.760552809483039</v>
+        <v>5.060613380186241</v>
       </c>
       <c r="U86">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V86">
         <v>0.265</v>
       </c>
       <c r="W86">
-        <v>0.05571300000000001</v>
+        <v>0.06615</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y86">
-        <v>2.018895363140179</v>
+        <v>1.680354321070085</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8876,22 +8876,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09596618390430964</v>
+        <v>0.09605725794452077</v>
       </c>
       <c r="C87">
-        <v>-37.3274568467757</v>
+        <v>-40.24505490489557</v>
       </c>
       <c r="D87">
-        <v>180.7575431532243</v>
+        <v>180.4829450951044</v>
       </c>
       <c r="E87">
-        <v>40.655</v>
+        <v>43.298</v>
       </c>
       <c r="F87">
-        <v>224.655</v>
+        <v>227.298</v>
       </c>
       <c r="G87">
         <v>6.57</v>
@@ -8912,28 +8912,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M87">
-        <v>20.21895</v>
+        <v>20.45682</v>
       </c>
       <c r="N87">
-        <v>13.75604999999999</v>
+        <v>13.51817999999999</v>
       </c>
       <c r="O87">
-        <v>3.645353249999999</v>
+        <v>3.582317699999999</v>
       </c>
       <c r="P87">
-        <v>10.11069675</v>
+        <v>9.935862299999995</v>
       </c>
       <c r="Q87">
-        <v>17.01069675</v>
+        <v>16.8358623</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2649245593620642</v>
+        <v>0.2797732710322913</v>
       </c>
       <c r="T87">
-        <v>5.060613380186241</v>
+        <v>5.403539746704187</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8950,7 +8950,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.680354321070085</v>
+        <v>1.660815317336712</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8958,22 +8958,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09605725794452077</v>
+        <v>0.09614833198473191</v>
       </c>
       <c r="C88">
-        <v>-40.24505490489557</v>
+        <v>-43.16181991654076</v>
       </c>
       <c r="D88">
-        <v>180.4829450951044</v>
+        <v>180.2091800834592</v>
       </c>
       <c r="E88">
-        <v>43.298</v>
+        <v>45.941</v>
       </c>
       <c r="F88">
-        <v>227.298</v>
+        <v>229.941</v>
       </c>
       <c r="G88">
         <v>6.57</v>
@@ -8994,28 +8994,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M88">
-        <v>20.45682</v>
+        <v>20.69469</v>
       </c>
       <c r="N88">
-        <v>13.51817999999999</v>
+        <v>13.28031</v>
       </c>
       <c r="O88">
-        <v>3.582317699999999</v>
+        <v>3.519282149999999</v>
       </c>
       <c r="P88">
-        <v>9.935862299999995</v>
+        <v>9.761027849999998</v>
       </c>
       <c r="Q88">
-        <v>16.8358623</v>
+        <v>16.66102785</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2797732710322913</v>
+        <v>0.2969063998825532</v>
       </c>
       <c r="T88">
-        <v>5.403539746704187</v>
+        <v>5.799224015763353</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -9032,7 +9032,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.660815317336712</v>
+        <v>1.641725486102957</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -9040,22 +9040,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09614833198473191</v>
+        <v>0.09623940602494305</v>
       </c>
       <c r="C89">
-        <v>-43.16181991654076</v>
+        <v>-46.077755666782</v>
       </c>
       <c r="D89">
-        <v>180.2091800834592</v>
+        <v>179.936244333218</v>
       </c>
       <c r="E89">
-        <v>45.941</v>
+        <v>48.584</v>
       </c>
       <c r="F89">
-        <v>229.941</v>
+        <v>232.584</v>
       </c>
       <c r="G89">
         <v>6.57</v>
@@ -9076,28 +9076,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M89">
-        <v>20.69469</v>
+        <v>20.93256</v>
       </c>
       <c r="N89">
-        <v>13.28031</v>
+        <v>13.04244</v>
       </c>
       <c r="O89">
-        <v>3.519282149999999</v>
+        <v>3.456246599999999</v>
       </c>
       <c r="P89">
-        <v>9.761027849999998</v>
+        <v>9.586193399999996</v>
       </c>
       <c r="Q89">
-        <v>16.66102785</v>
+        <v>16.4861934</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2969063998825532</v>
+        <v>0.3168950502078588</v>
       </c>
       <c r="T89">
-        <v>5.799224015763353</v>
+        <v>6.260855662999049</v>
       </c>
       <c r="U89">
         <v>0.09</v>
@@ -9114,7 +9114,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.641725486102957</v>
+        <v>1.623069514669969</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -9122,22 +9122,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09623940602494305</v>
+        <v>0.0963304800651542</v>
       </c>
       <c r="C90">
-        <v>-46.077755666782</v>
+        <v>-48.99286591779398</v>
       </c>
       <c r="D90">
-        <v>179.936244333218</v>
+        <v>179.664134082206</v>
       </c>
       <c r="E90">
-        <v>48.584</v>
+        <v>51.227</v>
       </c>
       <c r="F90">
-        <v>232.584</v>
+        <v>235.227</v>
       </c>
       <c r="G90">
         <v>6.57</v>
@@ -9158,28 +9158,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M90">
-        <v>20.93256</v>
+        <v>21.17043</v>
       </c>
       <c r="N90">
-        <v>13.04244</v>
+        <v>12.80456999999999</v>
       </c>
       <c r="O90">
-        <v>3.456246599999999</v>
+        <v>3.393211049999999</v>
       </c>
       <c r="P90">
-        <v>9.586193399999996</v>
+        <v>9.411358949999997</v>
       </c>
       <c r="Q90">
-        <v>16.4861934</v>
+        <v>16.31135895</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3168950502078588</v>
+        <v>0.3405180005923109</v>
       </c>
       <c r="T90">
-        <v>6.260855662999049</v>
+        <v>6.80642033700487</v>
       </c>
       <c r="U90">
         <v>0.09</v>
@@ -9196,7 +9196,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.623069514669969</v>
+        <v>1.604832778550081</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -9204,22 +9204,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.0963304800651542</v>
+        <v>0.09642155410536533</v>
       </c>
       <c r="C91">
-        <v>-48.99286591779398</v>
+        <v>-51.90715440902812</v>
       </c>
       <c r="D91">
-        <v>179.664134082206</v>
+        <v>179.3928455909719</v>
       </c>
       <c r="E91">
-        <v>51.227</v>
+        <v>53.87</v>
       </c>
       <c r="F91">
-        <v>235.227</v>
+        <v>237.87</v>
       </c>
       <c r="G91">
         <v>6.57</v>
@@ -9240,28 +9240,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M91">
-        <v>21.17043</v>
+        <v>21.4083</v>
       </c>
       <c r="N91">
-        <v>12.80456999999999</v>
+        <v>12.56669999999999</v>
       </c>
       <c r="O91">
-        <v>3.393211049999999</v>
+        <v>3.330175499999998</v>
       </c>
       <c r="P91">
-        <v>9.411358949999997</v>
+        <v>9.236524499999994</v>
       </c>
       <c r="Q91">
-        <v>16.31135895</v>
+        <v>16.1365245</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3405180005923109</v>
+        <v>0.3688655410536534</v>
       </c>
       <c r="T91">
-        <v>6.80642033700487</v>
+        <v>7.461097945811856</v>
       </c>
       <c r="U91">
         <v>0.09</v>
@@ -9278,7 +9278,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.604832778550081</v>
+        <v>1.587001303232858</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9286,22 +9286,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09642155410536533</v>
+        <v>0.09651262814557646</v>
       </c>
       <c r="C92">
-        <v>-51.90715440902812</v>
+        <v>-54.82062485738416</v>
       </c>
       <c r="D92">
-        <v>179.3928455909719</v>
+        <v>179.1223751426159</v>
       </c>
       <c r="E92">
-        <v>53.87</v>
+        <v>56.51300000000001</v>
       </c>
       <c r="F92">
-        <v>237.87</v>
+        <v>240.513</v>
       </c>
       <c r="G92">
         <v>6.57</v>
@@ -9322,28 +9322,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M92">
-        <v>21.4083</v>
+        <v>21.64617</v>
       </c>
       <c r="N92">
-        <v>12.56669999999999</v>
+        <v>12.32883</v>
       </c>
       <c r="O92">
-        <v>3.330175499999998</v>
+        <v>3.267139949999999</v>
       </c>
       <c r="P92">
-        <v>9.236524499999994</v>
+        <v>9.061690049999997</v>
       </c>
       <c r="Q92">
-        <v>16.1365245</v>
+        <v>15.96169005</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3688655410536534</v>
+        <v>0.4035125349508498</v>
       </c>
       <c r="T92">
-        <v>7.461097945811856</v>
+        <v>8.261259467687061</v>
       </c>
       <c r="U92">
         <v>0.09</v>
@@ -9360,7 +9360,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.587001303232858</v>
+        <v>1.569561728472058</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9368,22 +9368,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09651262814557646</v>
+        <v>0.09660370218578762</v>
       </c>
       <c r="C93">
-        <v>-54.82062485738416</v>
+        <v>-57.73328095737983</v>
       </c>
       <c r="D93">
-        <v>179.1223751426159</v>
+        <v>178.8527190426202</v>
       </c>
       <c r="E93">
-        <v>56.51300000000001</v>
+        <v>59.15600000000003</v>
       </c>
       <c r="F93">
-        <v>240.513</v>
+        <v>243.156</v>
       </c>
       <c r="G93">
         <v>6.57</v>
@@ -9404,28 +9404,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M93">
-        <v>21.64617</v>
+        <v>21.88404</v>
       </c>
       <c r="N93">
-        <v>12.32883</v>
+        <v>12.09095999999999</v>
       </c>
       <c r="O93">
-        <v>3.267139949999999</v>
+        <v>3.204104399999998</v>
       </c>
       <c r="P93">
-        <v>9.061690049999997</v>
+        <v>8.886855599999993</v>
       </c>
       <c r="Q93">
-        <v>15.96169005</v>
+        <v>15.7868556</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4035125349508498</v>
+        <v>0.4468212773223454</v>
       </c>
       <c r="T93">
-        <v>8.261259467687061</v>
+        <v>9.261461370031071</v>
       </c>
       <c r="U93">
         <v>0.09</v>
@@ -9442,7 +9442,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.569561728472058</v>
+        <v>1.552501274901709</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9450,22 +9450,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09660370218578762</v>
+        <v>0.09669477622599876</v>
       </c>
       <c r="C94">
-        <v>-57.73328095737983</v>
+        <v>-60.64512638131845</v>
       </c>
       <c r="D94">
-        <v>178.8527190426202</v>
+        <v>178.5838736186816</v>
       </c>
       <c r="E94">
-        <v>59.15600000000003</v>
+        <v>61.79900000000004</v>
       </c>
       <c r="F94">
-        <v>243.156</v>
+        <v>245.799</v>
       </c>
       <c r="G94">
         <v>6.57</v>
@@ -9486,28 +9486,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M94">
-        <v>21.88404</v>
+        <v>22.12191</v>
       </c>
       <c r="N94">
-        <v>12.09095999999999</v>
+        <v>11.85308999999999</v>
       </c>
       <c r="O94">
-        <v>3.204104399999998</v>
+        <v>3.141068849999998</v>
       </c>
       <c r="P94">
-        <v>8.886855599999993</v>
+        <v>8.712021149999993</v>
       </c>
       <c r="Q94">
-        <v>15.7868556</v>
+        <v>15.61202115</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4468212773223454</v>
+        <v>0.5025039460856967</v>
       </c>
       <c r="T94">
-        <v>9.261461370031071</v>
+        <v>10.54743524447337</v>
       </c>
       <c r="U94">
         <v>0.09</v>
@@ -9524,7 +9524,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.552501274901709</v>
+        <v>1.535807712805991</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9532,22 +9532,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09669477622599876</v>
+        <v>0.09678585026620989</v>
       </c>
       <c r="C95">
-        <v>-60.64512638131845</v>
+        <v>-63.55616477945659</v>
       </c>
       <c r="D95">
-        <v>178.5838736186816</v>
+        <v>178.3158352205434</v>
       </c>
       <c r="E95">
-        <v>61.79900000000004</v>
+        <v>64.44200000000004</v>
       </c>
       <c r="F95">
-        <v>245.799</v>
+        <v>248.442</v>
       </c>
       <c r="G95">
         <v>6.57</v>
@@ -9568,28 +9568,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M95">
-        <v>22.12191</v>
+        <v>22.35978</v>
       </c>
       <c r="N95">
-        <v>11.85308999999999</v>
+        <v>11.61521999999999</v>
       </c>
       <c r="O95">
-        <v>3.141068849999998</v>
+        <v>3.078033299999999</v>
       </c>
       <c r="P95">
-        <v>8.712021149999993</v>
+        <v>8.537186699999996</v>
       </c>
       <c r="Q95">
-        <v>15.61202115</v>
+        <v>15.4371867</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5025039460856967</v>
+        <v>0.5767475044368319</v>
       </c>
       <c r="T95">
-        <v>10.54743524447337</v>
+        <v>12.26206707706309</v>
       </c>
       <c r="U95">
         <v>0.09</v>
@@ -9606,7 +9606,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.535807712805991</v>
+        <v>1.519469332882524</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9614,22 +9614,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09678585026620989</v>
+        <v>0.09687692430642103</v>
       </c>
       <c r="C96">
-        <v>-63.55616477945659</v>
+        <v>-66.46639978016873</v>
       </c>
       <c r="D96">
-        <v>178.3158352205434</v>
+        <v>178.0486002198313</v>
       </c>
       <c r="E96">
-        <v>64.44200000000004</v>
+        <v>67.08500000000004</v>
       </c>
       <c r="F96">
-        <v>248.442</v>
+        <v>251.085</v>
       </c>
       <c r="G96">
         <v>6.57</v>
@@ -9650,28 +9650,28 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M96">
-        <v>22.35978</v>
+        <v>22.59765</v>
       </c>
       <c r="N96">
-        <v>11.61521999999999</v>
+        <v>11.37734999999999</v>
       </c>
       <c r="O96">
-        <v>3.078033299999999</v>
+        <v>3.014997749999998</v>
       </c>
       <c r="P96">
-        <v>8.537186699999996</v>
+        <v>8.362352249999994</v>
       </c>
       <c r="Q96">
-        <v>15.4371867</v>
+        <v>15.26235225</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5767475044368319</v>
+        <v>0.6806884861284213</v>
       </c>
       <c r="T96">
-        <v>12.26206707706309</v>
+        <v>14.66255164268872</v>
       </c>
       <c r="U96">
         <v>0.09</v>
@@ -9688,7 +9688,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.519469332882524</v>
+        <v>1.503474918852181</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9696,22 +9696,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09687692430642103</v>
+        <v>0.1412751992557446</v>
       </c>
       <c r="C97">
-        <v>-66.46639978016873</v>
+        <v>-144.2749409415622</v>
       </c>
       <c r="D97">
-        <v>178.0486002198313</v>
+        <v>102.8830590584378</v>
       </c>
       <c r="E97">
-        <v>67.08500000000004</v>
+        <v>69.72800000000004</v>
       </c>
       <c r="F97">
-        <v>251.085</v>
+        <v>253.728</v>
       </c>
       <c r="G97">
         <v>6.57</v>
@@ -9732,45 +9732,45 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M97">
-        <v>22.59765</v>
+        <v>37.24727040000001</v>
       </c>
       <c r="N97">
-        <v>11.37734999999999</v>
+        <v>-3.272270400000018</v>
       </c>
       <c r="O97">
-        <v>3.014997749999998</v>
+        <v>-0.8671516560000048</v>
       </c>
       <c r="P97">
-        <v>8.362352249999994</v>
+        <v>-2.405118744000013</v>
       </c>
       <c r="Q97">
-        <v>15.26235225</v>
+        <v>4.494881255999989</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6806884861284213</v>
+        <v>0.8603045557409469</v>
       </c>
       <c r="T97">
-        <v>14.66255164268872</v>
+        <v>18.81072876999878</v>
       </c>
       <c r="U97">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.265</v>
+        <v>0.2417190549350965</v>
       </c>
       <c r="W97">
-        <v>0.06615</v>
+        <v>0.1113156427355278</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y97">
-        <v>1.503474918852181</v>
+        <v>0.9121473771135719</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9778,22 +9778,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1412751992557445</v>
+        <v>0.1422851992557445</v>
       </c>
       <c r="C98">
-        <v>-144.2749409415622</v>
+        <v>-147.8965933447589</v>
       </c>
       <c r="D98">
-        <v>102.8830590584378</v>
+        <v>101.9044066552411</v>
       </c>
       <c r="E98">
-        <v>69.72800000000001</v>
+        <v>72.37099999999998</v>
       </c>
       <c r="F98">
-        <v>253.728</v>
+        <v>256.371</v>
       </c>
       <c r="G98">
         <v>6.57</v>
@@ -9814,37 +9814,37 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M98">
-        <v>37.2472704</v>
+        <v>37.6352628</v>
       </c>
       <c r="N98">
-        <v>-3.272270400000011</v>
+        <v>-3.660262800000005</v>
       </c>
       <c r="O98">
-        <v>-0.8671516560000029</v>
+        <v>-0.9699696420000015</v>
       </c>
       <c r="P98">
-        <v>-2.405118744000008</v>
+        <v>-2.690293158000004</v>
       </c>
       <c r="Q98">
-        <v>4.494881255999994</v>
+        <v>4.209706841999998</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8603045557409448</v>
+        <v>1.13180607432126</v>
       </c>
       <c r="T98">
-        <v>18.81072876999873</v>
+        <v>25.08097169333163</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.2417190549350966</v>
+        <v>0.2392271059151472</v>
       </c>
       <c r="W98">
-        <v>0.1113156427355278</v>
+        <v>0.1116814608516564</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.9121473771135721</v>
+        <v>0.9027437959062158</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9860,22 +9860,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1422851992557445</v>
+        <v>0.1432951992557445</v>
       </c>
       <c r="C99">
-        <v>-147.8965933447589</v>
+        <v>-151.4998027526919</v>
       </c>
       <c r="D99">
-        <v>101.9044066552411</v>
+        <v>100.9441972473081</v>
       </c>
       <c r="E99">
-        <v>72.37099999999998</v>
+        <v>75.01400000000001</v>
       </c>
       <c r="F99">
-        <v>256.371</v>
+        <v>259.014</v>
       </c>
       <c r="G99">
         <v>6.57</v>
@@ -9896,37 +9896,37 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M99">
-        <v>37.6352628</v>
+        <v>38.02325520000001</v>
       </c>
       <c r="N99">
-        <v>-3.660262800000005</v>
+        <v>-4.048255200000014</v>
       </c>
       <c r="O99">
-        <v>-0.9699696420000015</v>
+        <v>-1.072787628000004</v>
       </c>
       <c r="P99">
-        <v>-2.690293158000004</v>
+        <v>-2.97546757200001</v>
       </c>
       <c r="Q99">
-        <v>4.209706841999998</v>
+        <v>3.924532427999992</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.13180607432126</v>
+        <v>1.67480911148189</v>
       </c>
       <c r="T99">
-        <v>25.08097169333163</v>
+        <v>37.62145753999746</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.2392271059151472</v>
+        <v>0.2367860129976456</v>
       </c>
       <c r="W99">
-        <v>0.1116814608516564</v>
+        <v>0.1120398132919456</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9934,7 +9934,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.9027437959062158</v>
+        <v>0.8935321245194174</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9942,22 +9942,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1432951992557445</v>
+        <v>0.1443051992557445</v>
       </c>
       <c r="C100">
-        <v>-151.4998027526919</v>
+        <v>-155.085085644348</v>
       </c>
       <c r="D100">
-        <v>100.9441972473081</v>
+        <v>100.001914355652</v>
       </c>
       <c r="E100">
-        <v>75.01400000000001</v>
+        <v>77.65699999999998</v>
       </c>
       <c r="F100">
-        <v>259.014</v>
+        <v>261.657</v>
       </c>
       <c r="G100">
         <v>6.57</v>
@@ -9978,37 +9978,37 @@
         <v>33.97499999999999</v>
       </c>
       <c r="M100">
-        <v>38.02325520000001</v>
+        <v>38.4112476</v>
       </c>
       <c r="N100">
-        <v>-4.048255200000014</v>
+        <v>-4.436247600000009</v>
       </c>
       <c r="O100">
-        <v>-1.072787628000004</v>
+        <v>-1.175605614000002</v>
       </c>
       <c r="P100">
-        <v>-2.97546757200001</v>
+        <v>-3.260641986000006</v>
       </c>
       <c r="Q100">
-        <v>3.924532427999992</v>
+        <v>3.639358013999996</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.67480911148189</v>
+        <v>3.303818222963779</v>
       </c>
       <c r="T100">
-        <v>37.62145753999746</v>
+        <v>75.2429150799949</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.2367860129976456</v>
+        <v>0.2343942350885785</v>
       </c>
       <c r="W100">
-        <v>0.1120398132919456</v>
+        <v>0.1123909262889967</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -10016,91 +10016,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8935321245194174</v>
+        <v>0.8845065475040699</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1443051992557445</v>
-      </c>
-      <c r="C101">
-        <v>-155.085085644348</v>
-      </c>
-      <c r="D101">
-        <v>100.001914355652</v>
-      </c>
-      <c r="E101">
-        <v>77.65699999999998</v>
-      </c>
-      <c r="F101">
-        <v>261.657</v>
-      </c>
-      <c r="G101">
-        <v>6.57</v>
-      </c>
-      <c r="H101">
-        <v>80.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>40.875</v>
-      </c>
-      <c r="K101">
-        <v>6.900000000000002</v>
-      </c>
-      <c r="L101">
-        <v>33.97499999999999</v>
-      </c>
-      <c r="M101">
-        <v>38.4112476</v>
-      </c>
-      <c r="N101">
-        <v>-4.436247600000009</v>
-      </c>
-      <c r="O101">
-        <v>-1.175605614000002</v>
-      </c>
-      <c r="P101">
-        <v>-3.260641986000006</v>
-      </c>
-      <c r="Q101">
-        <v>3.639358013999996</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.303818222963779</v>
-      </c>
-      <c r="T101">
-        <v>75.2429150799949</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.2343942350885785</v>
-      </c>
-      <c r="W101">
-        <v>0.1123909262889967</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8845065475040699</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
